--- a/docs/deliverables/out/Drop-2_Independent/BRD-07_Claims/BIBS_TestPlan_BRD-07_Claims_v1.0.xlsx
+++ b/docs/deliverables/out/Drop-2_Independent/BRD-07_Claims/BIBS_TestPlan_BRD-07_Claims_v1.0.xlsx
@@ -16,11 +16,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Data" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roles and Access" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRS Findings" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_lists" sheetId="11" state="hidden" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_lists" sheetId="10" state="hidden" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$65</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'README'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Document Control'!$A$4:$F$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Document Control'!$4:$4</definedName>
@@ -28,16 +27,14 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Test Conditions'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Scenarios'!$A$4:$F$12</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Scenarios'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Test Cases'!$A$4:$R$189</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Test Cases'!$A$4:$Q$189</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Test Cases'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Coverage'!$A$4:$J$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Coverage'!$A$4:$I$95</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Coverage'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Test Data'!$A$4:$E$13</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Test Data'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Roles and Access'!$A$4:$M$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Roles and Access'!$A$4:$L$89</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Roles and Access'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'FRS Findings'!$A$4:$D$11</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="9">'FRS Findings'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -438,7 +435,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>38</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="971550" cy="285750"/>
@@ -751,7 +748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B4:E39"/>
+  <dimension ref="B4:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1010,92 +1007,77 @@
         <v>85</v>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>FRS Findings</t>
-        </is>
-      </c>
-      <c r="C28" s="12" t="inlineStr">
-        <is>
-          <t>FRS points raised for the FRS owner; the affected cases assume the proposed resolution</t>
-        </is>
-      </c>
-      <c r="D28" s="12" t="n">
-        <v>7</v>
+    <row r="29">
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>Legend</t>
+        </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>Legend</t>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>The case ran and the actual result matches the expected result</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="15" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
         <is>
-          <t>The case ran and the actual result matches the expected result</t>
+          <t>The actual result differs; an issue ID is recorded</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="C32" s="16" t="inlineStr">
         <is>
-          <t>The actual result differs; a defect ID is recorded</t>
+          <t>The case cannot run (environment, data or an open issue elsewhere)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="17" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="B33" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C33" s="16" t="inlineStr">
         <is>
-          <t>The case cannot run (environment, data or a defect elsewhere)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C34" s="16" t="inlineStr">
-        <is>
           <t>Not applicable in this cycle, with the reason in Actual result</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>Source: FRS BRD-7 Claims. 39 FRs, 52 BRD IDs, 136 test conditions, 8 scenarios, 185 test cases (107 positive, 78 negative).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="19" t="inlineStr">
         <is>
-          <t>Source: FRS BRD-7 (FRS_BRD07_CLAIMS.md). 39 FRs, 52 BRD IDs, 136 test conditions, 8 scenarios, 185 test cases (107 positive, 78 negative), 0 with an automation reference.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="19" t="inlineStr">
-        <is>
-          <t>Status starts as Not run. Testers fill Status, Actual result, Tester, Date and Defect ID during execution.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="26" customHeight="1">
-      <c r="B39" s="20" t="inlineStr">
+          <t>Status starts as Not run. Testers fill Status, Actual result, Tester, Date and Issue ID during execution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="B38" s="20" t="inlineStr">
         <is>
           <t>Prepared by iorta TechNXT for BDOI. Confidential – BDOI.</t>
         </is>
@@ -1111,7 +1093,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId9"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
@@ -1124,7 +1105,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
 </worksheet>
 </file>
 
@@ -1132,244 +1113,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="21" t="inlineStr">
-        <is>
-          <t>FRS Findings</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="24" t="inlineStr">
-        <is>
-          <t>FRS points raised for the FRS owner; the affected cases assume the proposed resolution</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="6" customHeight="1">
-      <c r="A3" s="25" t="n"/>
-      <c r="B3" s="25" t="n"/>
-      <c r="C3" s="25" t="n"/>
-      <c r="D3" s="25" t="n"/>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="26" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B4" s="26" t="inlineStr">
-        <is>
-          <t>FR ID</t>
-        </is>
-      </c>
-      <c r="C4" s="26" t="inlineStr">
-        <is>
-          <t>Finding</t>
-        </is>
-      </c>
-      <c r="D4" s="26" t="inlineStr">
-        <is>
-          <t>Proposed resolution</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>TF-CM-01</t>
-        </is>
-      </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>FR-CM-001</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>The FRS messages "Invalid user ID or password" and "Your account is locked. Contact the System Administrator" differ from the platform log-in ("Invalid user name or password"; "Account is locked. Contact your administrator."). The idle timeout of 15 minutes differs from the BIBS session policy (CLQ24).</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>Quote the platform texts in FRS v1.1 and close CLQ24; the cases use the platform texts and a 15-minute test setting.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>TF-CM-02</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>FR-CM-024</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>The FRS pairs EMAIL_ADDRESS_INVALID with "Enter a valid e-mail address"; the platform returns "Invalid e-mail address - &lt;address&gt;" for that code.</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>Quote the platform text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>TF-CM-03</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>FR-CM-060</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>FR-CM-060 to 066 pair INVALID_REPORT_PARAMETERS with FRS texts ("The as-of date cannot be in the future", "The end date must be on or after the start date"). The report engine builds its own texts from the parameter labels, for example "&lt;to&gt; must not be before &lt;from&gt;". The future as-of date check does not exist in the engine today.</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>Quote the engine texts, and add the as-of date rule to the report definition at build; the range cases use the engine pattern, TC-CM-060.3-01 uses the FRS text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>TF-CM-04</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>FR-CM-012</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>Acceptance criterion 3 says a Claims Officer without BCL_STATUS_UPDATE cannot correct the date, but the matrix of section 3.3 grants BCL_STATUS_UPDATE to officers (within the matrix). As written every officer can correct the reported date.</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>State whether the correction needs its own permission or is limited to TL / TH (CLQ03); the case removes the permission from a test role until then.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>TF-CM-05</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>FR-CM-045</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>The persona table gives reopen to the Team Head (CLM_TH) and the matrix gives BCL_REOPEN to TH and UH, while R1 says "TH / UH reopen (to confirm, CLQ06)". Temporarily closed claims keep ageing "to confirm" (R2 of FR-CM-053), so the ageing and outstanding cases depend on CLQ06.</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>Close CLQ06 before UAT.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>TF-CM-06</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>FR-CM-043</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>Two settlement types ("Settled - LOA Issued - For Schedule of Repair", "... Vehicle Under Repair") have "Closes the claim" to confirm (CLQ05), so their closure behaviour cannot be tested yet.</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Answer CLQ05; the cases treat both as not closing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>TF-CM-07</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>FR-CM-016</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>The meaning of the claims authorization code and any TL / TH override are open (CLQ01); the FRS tests only that the button is disabled while premium is unpaid.</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>Answer CLQ01 before UAT and add the override case if one is agreed.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A4:D11"/>
-  <mergeCells count="1">
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <conditionalFormatting sqref="A5:D511">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Plan BRD-7 Claims&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
-    <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1518,6 +1264,20 @@
       <c r="B7" t="inlineStr">
         <is>
           <t>Upload-download</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Message</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D72"/>
+  <dimension ref="A1:D65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2013,7 +1773,7 @@
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>Positive, Negative, Boundary, Security-access, Workflow, Report-output, Upload-download</t>
+          <t>Positive, Negative, Boundary, Security-access, Workflow, Report-output, Upload-download, Screen, Message</t>
         </is>
       </c>
     </row>
@@ -2030,7 +1790,7 @@
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Role code and name (and SIT/UAT user for built BRDs)</t>
+          <t>Role code and name (and the SIT/UAT user)</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr"/>
@@ -2102,7 +1862,7 @@
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>What the system must do, with the exact message text and, for built BRDs, its code</t>
+          <t>What the system must do, with the exact message text and, where the system shows one, its code</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr"/>
@@ -2137,15 +1897,19 @@
       </c>
       <c r="B35" s="22" t="inlineStr">
         <is>
-          <t>Automation reference</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Existing automated test (class#method) that covers the case; blank when none</t>
-        </is>
-      </c>
-      <c r="D35" s="12" t="inlineStr"/>
+          <t>Execution status</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>Not run, Pass, Fail, Blocked, N/A</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
@@ -2155,19 +1919,15 @@
       </c>
       <c r="B36" s="23" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Actual result</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>Execution status</t>
-        </is>
-      </c>
-      <c r="D36" s="14" t="inlineStr">
-        <is>
-          <t>Not run, Pass, Fail, Blocked, N/A</t>
-        </is>
-      </c>
+          <t>What happened, filled by the tester</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
@@ -2177,12 +1937,12 @@
       </c>
       <c r="B37" s="22" t="inlineStr">
         <is>
-          <t>Actual result</t>
+          <t>Tester</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>What happened, filled by the tester</t>
+          <t>Who ran the case</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr"/>
@@ -2195,12 +1955,12 @@
       </c>
       <c r="B38" s="23" t="inlineStr">
         <is>
-          <t>Tester</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>Who ran the case</t>
+          <t>Date of the run</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr"/>
@@ -2213,12 +1973,12 @@
       </c>
       <c r="B39" s="22" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Issue ID</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Date of the run</t>
+          <t>Issue raised when the case fails</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr"/>
@@ -2226,17 +1986,17 @@
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
         <is>
-          <t>Test Cases</t>
+          <t>Coverage</t>
         </is>
       </c>
       <c r="B40" s="23" t="inlineStr">
         <is>
-          <t>Defect ID</t>
+          <t>FR / BRD ID</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>Defect raised when the case fails</t>
+          <t>FR of the FRS, then BRD requirement ID</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr"/>
@@ -2249,12 +2009,12 @@
       </c>
       <c r="B41" s="22" t="inlineStr">
         <is>
-          <t>FR / BRD ID</t>
+          <t>Kind</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>FR of the FRS, then BRD requirement ID</t>
+          <t>FR or BRD ID</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr"/>
@@ -2267,12 +2027,12 @@
       </c>
       <c r="B42" s="23" t="inlineStr">
         <is>
-          <t>Kind</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>FR or BRD ID</t>
+          <t>FR title</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr"/>
@@ -2285,12 +2045,12 @@
       </c>
       <c r="B43" s="22" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Traces</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>FR title</t>
+          <t>BRD IDs of the FR, or FRs of the BRD ID</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr"/>
@@ -2303,12 +2063,12 @@
       </c>
       <c r="B44" s="23" t="inlineStr">
         <is>
-          <t>Traces</t>
+          <t>Conditions</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>BRD IDs of the FR, or FRs of the BRD ID</t>
+          <t>Test conditions</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr"/>
@@ -2321,12 +2081,12 @@
       </c>
       <c r="B45" s="22" t="inlineStr">
         <is>
-          <t>Conditions</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Test conditions</t>
+          <t>Cases where the action succeeds</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr"/>
@@ -2339,12 +2099,12 @@
       </c>
       <c r="B46" s="23" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>Cases where the action succeeds</t>
+          <t>Cases where BIBS refuses the action</t>
         </is>
       </c>
       <c r="D46" s="14" t="inlineStr"/>
@@ -2357,12 +2117,12 @@
       </c>
       <c r="B47" s="22" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Cases where BIBS refuses the action</t>
+          <t>All cases</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr"/>
@@ -2375,30 +2135,34 @@
       </c>
       <c r="B48" s="23" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Coverage</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>All cases</t>
-        </is>
-      </c>
-      <c r="D48" s="14" t="inlineStr"/>
+          <t>Covered: at least one positive and one negative case (FR) or one case (BRD ID); GAP otherwise</t>
+        </is>
+      </c>
+      <c r="D48" s="14" t="inlineStr">
+        <is>
+          <t>Covered, GAP</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>Coverage</t>
+          <t>Test Data</t>
         </is>
       </c>
       <c r="B49" s="22" t="inlineStr">
         <is>
-          <t>Automated</t>
+          <t>Data set</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Cases with an automation reference</t>
+          <t>Data set ID</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr"/>
@@ -2406,24 +2170,20 @@
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>Coverage</t>
+          <t>Test Data</t>
         </is>
       </c>
       <c r="B50" s="23" t="inlineStr">
         <is>
-          <t>Coverage</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>Covered: at least one positive and one negative case (FR) or one case (BRD ID); GAP otherwise</t>
-        </is>
-      </c>
-      <c r="D50" s="14" t="inlineStr">
-        <is>
-          <t>Covered, GAP</t>
-        </is>
-      </c>
+          <t>Short name used in the cases</t>
+        </is>
+      </c>
+      <c r="D50" s="14" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
@@ -2433,12 +2193,12 @@
       </c>
       <c r="B51" s="22" t="inlineStr">
         <is>
-          <t>Data set</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Data set ID</t>
+          <t>Records and values in the set</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr"/>
@@ -2451,12 +2211,12 @@
       </c>
       <c r="B52" s="23" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Source</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>Short name used in the cases</t>
+          <t>Seed data set that provides it, or how the tester prepares it; non-production data is masked</t>
         </is>
       </c>
       <c r="D52" s="14" t="inlineStr"/>
@@ -2469,12 +2229,12 @@
       </c>
       <c r="B53" s="22" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Cases</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Records and values in the set</t>
+          <t>Number of cases that use it</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr"/>
@@ -2482,17 +2242,17 @@
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>Test Data</t>
+          <t>Roles and Access</t>
         </is>
       </c>
       <c r="B54" s="23" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>Case ID</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Seed that provides it (built BRDs) or how to prepare it; non-production data is masked</t>
+          <t>Access case ID: AC-&lt;code&gt;-&lt;nn&gt;.&lt;n&gt;</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr"/>
@@ -2500,17 +2260,17 @@
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>Test Data</t>
+          <t>Roles and Access</t>
         </is>
       </c>
       <c r="B55" s="22" t="inlineStr">
         <is>
-          <t>Cases</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Number of cases that use it</t>
+          <t>Screen or action checked</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr"/>
@@ -2523,12 +2283,12 @@
       </c>
       <c r="B56" s="23" t="inlineStr">
         <is>
-          <t>Case ID</t>
+          <t>Screen (menu path)</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
         <is>
-          <t>Access case ID: AC-&lt;code&gt;-&lt;nn&gt;.&lt;n&gt;</t>
+          <t>Where it is done</t>
         </is>
       </c>
       <c r="D56" s="14" t="inlineStr"/>
@@ -2541,12 +2301,12 @@
       </c>
       <c r="B57" s="22" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Permission</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Screen or action checked</t>
+          <t>BIBS permission that grants it</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr"/>
@@ -2559,12 +2319,12 @@
       </c>
       <c r="B58" s="23" t="inlineStr">
         <is>
-          <t>Screen (menu path)</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>Where it is done</t>
+          <t>Role tested (log in as a user who holds only this role)</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr"/>
@@ -2577,15 +2337,19 @@
       </c>
       <c r="B59" s="22" t="inlineStr">
         <is>
-          <t>Permission</t>
+          <t>Access</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>BIBS permission that grants it</t>
-        </is>
-      </c>
-      <c r="D59" s="12" t="inlineStr"/>
+          <t>Expected access</t>
+        </is>
+      </c>
+      <c r="D59" s="12" t="inlineStr">
+        <is>
+          <t>Allowed, Denied</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="14" t="inlineStr">
@@ -2595,12 +2359,12 @@
       </c>
       <c r="B60" s="23" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Expected result</t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
-          <t>Role tested (log in as a user who holds only this role)</t>
+          <t>What the user sees</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr"/>
@@ -2613,17 +2377,17 @@
       </c>
       <c r="B61" s="22" t="inlineStr">
         <is>
-          <t>Access</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Expected access</t>
+          <t>Execution status</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>Allowed, Denied</t>
+          <t>Not run, Pass, Fail, Blocked, N/A</t>
         </is>
       </c>
     </row>
@@ -2635,12 +2399,12 @@
       </c>
       <c r="B62" s="23" t="inlineStr">
         <is>
-          <t>Expected result</t>
+          <t>Actual result</t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
         <is>
-          <t>What the user sees</t>
+          <t>Filled by the tester</t>
         </is>
       </c>
       <c r="D62" s="14" t="inlineStr"/>
@@ -2653,12 +2417,12 @@
       </c>
       <c r="B63" s="22" t="inlineStr">
         <is>
-          <t>Automation reference</t>
+          <t>Tester</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Existing automated test, if any</t>
+          <t>Who ran the case</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr"/>
@@ -2671,19 +2435,15 @@
       </c>
       <c r="B64" s="23" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
         <is>
-          <t>Execution status</t>
-        </is>
-      </c>
-      <c r="D64" s="14" t="inlineStr">
-        <is>
-          <t>Not run, Pass, Fail, Blocked, N/A</t>
-        </is>
-      </c>
+          <t>Date of the run</t>
+        </is>
+      </c>
+      <c r="D64" s="14" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
@@ -2693,144 +2453,18 @@
       </c>
       <c r="B65" s="22" t="inlineStr">
         <is>
-          <t>Actual result</t>
+          <t>Issue ID</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Filled by the tester</t>
+          <t>Issue raised when the case fails</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr"/>
     </row>
-    <row r="66">
-      <c r="A66" s="14" t="inlineStr">
-        <is>
-          <t>Roles and Access</t>
-        </is>
-      </c>
-      <c r="B66" s="23" t="inlineStr">
-        <is>
-          <t>Tester</t>
-        </is>
-      </c>
-      <c r="C66" s="14" t="inlineStr">
-        <is>
-          <t>Who ran the case</t>
-        </is>
-      </c>
-      <c r="D66" s="14" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="12" t="inlineStr">
-        <is>
-          <t>Roles and Access</t>
-        </is>
-      </c>
-      <c r="B67" s="22" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C67" s="12" t="inlineStr">
-        <is>
-          <t>Date of the run</t>
-        </is>
-      </c>
-      <c r="D67" s="12" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="14" t="inlineStr">
-        <is>
-          <t>Roles and Access</t>
-        </is>
-      </c>
-      <c r="B68" s="23" t="inlineStr">
-        <is>
-          <t>Defect ID</t>
-        </is>
-      </c>
-      <c r="C68" s="14" t="inlineStr">
-        <is>
-          <t>Defect raised when the case fails</t>
-        </is>
-      </c>
-      <c r="D68" s="14" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="12" t="inlineStr">
-        <is>
-          <t>FRS Findings</t>
-        </is>
-      </c>
-      <c r="B69" s="22" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="C69" s="12" t="inlineStr">
-        <is>
-          <t>Finding ID</t>
-        </is>
-      </c>
-      <c r="D69" s="12" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="14" t="inlineStr">
-        <is>
-          <t>FRS Findings</t>
-        </is>
-      </c>
-      <c r="B70" s="23" t="inlineStr">
-        <is>
-          <t>FR ID</t>
-        </is>
-      </c>
-      <c r="C70" s="14" t="inlineStr">
-        <is>
-          <t>FR concerned</t>
-        </is>
-      </c>
-      <c r="D70" s="14" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="12" t="inlineStr">
-        <is>
-          <t>FRS Findings</t>
-        </is>
-      </c>
-      <c r="B71" s="22" t="inlineStr">
-        <is>
-          <t>Finding</t>
-        </is>
-      </c>
-      <c r="C71" s="12" t="inlineStr">
-        <is>
-          <t>Ambiguous or untestable point found while writing the cases</t>
-        </is>
-      </c>
-      <c r="D71" s="12" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="14" t="inlineStr">
-        <is>
-          <t>FRS Findings</t>
-        </is>
-      </c>
-      <c r="B72" s="23" t="inlineStr">
-        <is>
-          <t>Proposed resolution</t>
-        </is>
-      </c>
-      <c r="C72" s="14" t="inlineStr">
-        <is>
-          <t>What the test team proposes to the FRS owner</t>
-        </is>
-      </c>
-      <c r="D72" s="14" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:D72"/>
+  <autoFilter ref="A4:D65"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
@@ -2940,7 +2574,7 @@
       <c r="E5" s="12" t="inlineStr"/>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>Internal draft from FRS BRD-7 v1.0 and the Claims build design</t>
+          <t>Internal draft from FRS BRD-7 v1.0</t>
         </is>
       </c>
     </row>
@@ -3249,7 +2883,7 @@
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Each Claims action is offered only to the roles holding its permission; a direct call without it is refused (HTTP 403) and logged.</t>
+          <t>Each Claims action is offered only to the roles holding its permission; a direct request without it is refused and logged.</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
@@ -5425,7 +5059,7 @@
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>A status outside the matrix is refused even when called directly.</t>
+          <t>A status outside the matrix is refused even when requested directly.</t>
         </is>
       </c>
       <c r="E78" s="12" t="inlineStr">
@@ -5681,7 +5315,7 @@
       </c>
       <c r="D86" s="12" t="inlineStr">
         <is>
-          <t>An attribute change takes effect after authorisation without a new build.</t>
+          <t>An attribute change takes effect after authorisation, without a change to the system.</t>
         </is>
       </c>
       <c r="E86" s="12" t="inlineStr">
@@ -7793,7 +7427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R189"/>
+  <dimension ref="A1:Q189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7808,12 +7442,11 @@
     <col width="52" customWidth="1" min="10" max="10"/>
     <col width="50" customWidth="1" min="11" max="11"/>
     <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="30" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -7848,7 +7481,6 @@
       <c r="O3" s="25" t="n"/>
       <c r="P3" s="25" t="n"/>
       <c r="Q3" s="25" t="n"/>
-      <c r="R3" s="25" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
@@ -7913,32 +7545,27 @@
       </c>
       <c r="M4" s="26" t="inlineStr">
         <is>
-          <t>Automation reference</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="N4" s="26" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Actual result</t>
         </is>
       </c>
       <c r="O4" s="26" t="inlineStr">
         <is>
-          <t>Actual result</t>
+          <t>Tester</t>
         </is>
       </c>
       <c r="P4" s="26" t="inlineStr">
         <is>
-          <t>Tester</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="Q4" s="26" t="inlineStr">
         <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="R4" s="26" t="inlineStr">
-        <is>
-          <t>Defect ID</t>
+          <t>Issue ID</t>
         </is>
       </c>
     </row>
@@ -8004,16 +7631,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M5" s="12" t="inlineStr"/>
-      <c r="N5" s="27" t="inlineStr">
+      <c r="M5" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N5" s="12" t="n"/>
       <c r="O5" s="12" t="n"/>
-      <c r="P5" s="12" t="n"/>
-      <c r="Q5" s="28" t="n"/>
-      <c r="R5" s="12" t="n"/>
+      <c r="P5" s="28" t="n"/>
+      <c r="Q5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
@@ -8077,16 +7703,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M6" s="12" t="inlineStr"/>
-      <c r="N6" s="27" t="inlineStr">
+      <c r="M6" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N6" s="12" t="n"/>
       <c r="O6" s="12" t="n"/>
-      <c r="P6" s="12" t="n"/>
-      <c r="Q6" s="28" t="n"/>
-      <c r="R6" s="12" t="n"/>
+      <c r="P6" s="28" t="n"/>
+      <c r="Q6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
@@ -8150,16 +7775,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M7" s="12" t="inlineStr"/>
-      <c r="N7" s="27" t="inlineStr">
+      <c r="M7" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N7" s="12" t="n"/>
       <c r="O7" s="12" t="n"/>
-      <c r="P7" s="12" t="n"/>
-      <c r="Q7" s="28" t="n"/>
-      <c r="R7" s="12" t="n"/>
+      <c r="P7" s="28" t="n"/>
+      <c r="Q7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
@@ -8222,16 +7846,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M8" s="12" t="inlineStr"/>
-      <c r="N8" s="27" t="inlineStr">
+      <c r="M8" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N8" s="12" t="n"/>
       <c r="O8" s="12" t="n"/>
-      <c r="P8" s="12" t="n"/>
-      <c r="Q8" s="28" t="n"/>
-      <c r="R8" s="12" t="n"/>
+      <c r="P8" s="28" t="n"/>
+      <c r="Q8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
@@ -8295,16 +7918,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M9" s="12" t="inlineStr"/>
-      <c r="N9" s="27" t="inlineStr">
+      <c r="M9" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N9" s="12" t="n"/>
       <c r="O9" s="12" t="n"/>
-      <c r="P9" s="12" t="n"/>
-      <c r="Q9" s="28" t="n"/>
-      <c r="R9" s="12" t="n"/>
+      <c r="P9" s="28" t="n"/>
+      <c r="Q9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
@@ -8368,16 +7990,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M10" s="12" t="inlineStr"/>
-      <c r="N10" s="27" t="inlineStr">
+      <c r="M10" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N10" s="12" t="n"/>
       <c r="O10" s="12" t="n"/>
-      <c r="P10" s="12" t="n"/>
-      <c r="Q10" s="28" t="n"/>
-      <c r="R10" s="12" t="n"/>
+      <c r="P10" s="28" t="n"/>
+      <c r="Q10" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
@@ -8428,12 +8049,12 @@
       <c r="J11" s="12" t="inlineStr">
         <is>
           <t>1. Open BCL-2026-000102; look for Set Settlement and Close.
-2. Call the close endpoint with cl.officer1's token.</t>
+2. Send a direct request to close the claim, signed in as cl.officer1.</t>
         </is>
       </c>
       <c r="K11" s="12" t="inlineStr">
         <is>
-          <t>The actions are not shown; the call returns HTTP 403 and is logged with user, endpoint and time.
+          <t>The actions are not shown; the request is refused and is logged with the user and time.
 Message "You are not permitted to perform this action".</t>
         </is>
       </c>
@@ -8442,16 +8063,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M11" s="12" t="inlineStr"/>
-      <c r="N11" s="27" t="inlineStr">
+      <c r="M11" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N11" s="12" t="n"/>
       <c r="O11" s="12" t="n"/>
-      <c r="P11" s="12" t="n"/>
-      <c r="Q11" s="28" t="n"/>
-      <c r="R11" s="12" t="n"/>
+      <c r="P11" s="28" t="n"/>
+      <c r="Q11" s="12" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
@@ -8514,16 +8134,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M12" s="12" t="inlineStr"/>
-      <c r="N12" s="27" t="inlineStr">
+      <c r="M12" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N12" s="12" t="n"/>
       <c r="O12" s="12" t="n"/>
-      <c r="P12" s="12" t="n"/>
-      <c r="Q12" s="28" t="n"/>
-      <c r="R12" s="12" t="n"/>
+      <c r="P12" s="28" t="n"/>
+      <c r="Q12" s="12" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
@@ -8573,12 +8192,12 @@
       </c>
       <c r="J13" s="12" t="inlineStr">
         <is>
-          <t>1. As cl.officer1 call the claimant override, reserve amendment and follow-up override endpoints.</t>
+          <t>1. As cl.officer1 send direct requests for the claimant override, the reserve amendment and the follow-up override.</t>
         </is>
       </c>
       <c r="K13" s="12" t="inlineStr">
         <is>
-          <t>Each call returns HTTP 403; the claim is unchanged.
+          <t>Each direct request is refused; the claim is unchanged.
 Message "You are not permitted to perform this action".</t>
         </is>
       </c>
@@ -8587,16 +8206,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M13" s="12" t="inlineStr"/>
-      <c r="N13" s="27" t="inlineStr">
+      <c r="M13" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N13" s="12" t="n"/>
       <c r="O13" s="12" t="n"/>
-      <c r="P13" s="12" t="n"/>
-      <c r="Q13" s="28" t="n"/>
-      <c r="R13" s="12" t="n"/>
+      <c r="P13" s="28" t="n"/>
+      <c r="Q13" s="12" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
@@ -8659,16 +8277,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M14" s="12" t="inlineStr"/>
-      <c r="N14" s="27" t="inlineStr">
+      <c r="M14" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N14" s="12" t="n"/>
       <c r="O14" s="12" t="n"/>
-      <c r="P14" s="12" t="n"/>
-      <c r="Q14" s="28" t="n"/>
-      <c r="R14" s="12" t="n"/>
+      <c r="P14" s="28" t="n"/>
+      <c r="Q14" s="12" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
@@ -8708,7 +8325,7 @@
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
-          <t>API call with the user's token (tester tool, for example Postman)</t>
+          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I15" s="12" t="inlineStr">
@@ -8718,12 +8335,12 @@
       </c>
       <c r="J15" s="12" t="inlineStr">
         <is>
-          <t>1. Call GET on a claim id of the second test company with cl.officer1's token.</t>
+          <t>1. Send a direct request to open a claim of the second test company, signed in as cl.officer1.</t>
         </is>
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
-          <t>The call answers not found and reveals no data.</t>
+          <t>The request answers not found and reveals no data.</t>
         </is>
       </c>
       <c r="L15" s="12" t="inlineStr">
@@ -8731,16 +8348,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M15" s="12" t="inlineStr"/>
-      <c r="N15" s="27" t="inlineStr">
+      <c r="M15" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N15" s="12" t="n"/>
       <c r="O15" s="12" t="n"/>
-      <c r="P15" s="12" t="n"/>
-      <c r="Q15" s="28" t="n"/>
-      <c r="R15" s="12" t="n"/>
+      <c r="P15" s="28" t="n"/>
+      <c r="Q15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
@@ -8803,16 +8419,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M16" s="12" t="inlineStr"/>
-      <c r="N16" s="27" t="inlineStr">
+      <c r="M16" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N16" s="12" t="n"/>
       <c r="O16" s="12" t="n"/>
-      <c r="P16" s="12" t="n"/>
-      <c r="Q16" s="28" t="n"/>
-      <c r="R16" s="12" t="n"/>
+      <c r="P16" s="28" t="n"/>
+      <c r="Q16" s="12" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
@@ -8875,16 +8490,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M17" s="12" t="inlineStr"/>
-      <c r="N17" s="27" t="inlineStr">
+      <c r="M17" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N17" s="12" t="n"/>
       <c r="O17" s="12" t="n"/>
-      <c r="P17" s="12" t="n"/>
-      <c r="Q17" s="28" t="n"/>
-      <c r="R17" s="12" t="n"/>
+      <c r="P17" s="28" t="n"/>
+      <c r="Q17" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
@@ -8947,16 +8561,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M18" s="12" t="inlineStr"/>
-      <c r="N18" s="27" t="inlineStr">
+      <c r="M18" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N18" s="12" t="n"/>
       <c r="O18" s="12" t="n"/>
-      <c r="P18" s="12" t="n"/>
-      <c r="Q18" s="28" t="n"/>
-      <c r="R18" s="12" t="n"/>
+      <c r="P18" s="28" t="n"/>
+      <c r="Q18" s="12" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
@@ -8996,7 +8609,7 @@
       </c>
       <c r="H19" s="12" t="inlineStr">
         <is>
-          <t>API call with the user's token (tester tool, for example Postman)</t>
+          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I19" s="12" t="inlineStr">
@@ -9006,12 +8619,12 @@
       </c>
       <c r="J19" s="12" t="inlineStr">
         <is>
-          <t>1. Look for edit or delete on the History tab; call PUT and DELETE on a history row.</t>
+          <t>1. Look for edit or delete on the History tab; send direct requests to change and to delete a history row.</t>
         </is>
       </c>
       <c r="K19" s="12" t="inlineStr">
         <is>
-          <t>No action exists; the calls are refused.</t>
+          <t>No action exists; direct requests are refused.</t>
         </is>
       </c>
       <c r="L19" s="12" t="inlineStr">
@@ -9019,16 +8632,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M19" s="12" t="inlineStr"/>
-      <c r="N19" s="27" t="inlineStr">
+      <c r="M19" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N19" s="12" t="n"/>
       <c r="O19" s="12" t="n"/>
-      <c r="P19" s="12" t="n"/>
-      <c r="Q19" s="28" t="n"/>
-      <c r="R19" s="12" t="n"/>
+      <c r="P19" s="28" t="n"/>
+      <c r="Q19" s="12" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
@@ -9091,16 +8703,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M20" s="12" t="inlineStr"/>
-      <c r="N20" s="27" t="inlineStr">
+      <c r="M20" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N20" s="12" t="n"/>
       <c r="O20" s="12" t="n"/>
-      <c r="P20" s="12" t="n"/>
-      <c r="Q20" s="28" t="n"/>
-      <c r="R20" s="12" t="n"/>
+      <c r="P20" s="28" t="n"/>
+      <c r="Q20" s="12" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
@@ -9163,16 +8774,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M21" s="12" t="inlineStr"/>
-      <c r="N21" s="27" t="inlineStr">
+      <c r="M21" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N21" s="12" t="n"/>
       <c r="O21" s="12" t="n"/>
-      <c r="P21" s="12" t="n"/>
-      <c r="Q21" s="28" t="n"/>
-      <c r="R21" s="12" t="n"/>
+      <c r="P21" s="28" t="n"/>
+      <c r="Q21" s="12" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
@@ -9235,16 +8845,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M22" s="12" t="inlineStr"/>
-      <c r="N22" s="27" t="inlineStr">
+      <c r="M22" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N22" s="12" t="n"/>
       <c r="O22" s="12" t="n"/>
-      <c r="P22" s="12" t="n"/>
-      <c r="Q22" s="28" t="n"/>
-      <c r="R22" s="12" t="n"/>
+      <c r="P22" s="28" t="n"/>
+      <c r="Q22" s="12" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
@@ -9308,16 +8917,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M23" s="12" t="inlineStr"/>
-      <c r="N23" s="27" t="inlineStr">
+      <c r="M23" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N23" s="12" t="n"/>
       <c r="O23" s="12" t="n"/>
-      <c r="P23" s="12" t="n"/>
-      <c r="Q23" s="28" t="n"/>
-      <c r="R23" s="12" t="n"/>
+      <c r="P23" s="28" t="n"/>
+      <c r="Q23" s="12" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
@@ -9380,16 +8988,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M24" s="12" t="inlineStr"/>
-      <c r="N24" s="27" t="inlineStr">
+      <c r="M24" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N24" s="12" t="n"/>
       <c r="O24" s="12" t="n"/>
-      <c r="P24" s="12" t="n"/>
-      <c r="Q24" s="28" t="n"/>
-      <c r="R24" s="12" t="n"/>
+      <c r="P24" s="28" t="n"/>
+      <c r="Q24" s="12" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
@@ -9453,16 +9060,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M25" s="12" t="inlineStr"/>
-      <c r="N25" s="27" t="inlineStr">
+      <c r="M25" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N25" s="12" t="n"/>
       <c r="O25" s="12" t="n"/>
-      <c r="P25" s="12" t="n"/>
-      <c r="Q25" s="28" t="n"/>
-      <c r="R25" s="12" t="n"/>
+      <c r="P25" s="28" t="n"/>
+      <c r="Q25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
@@ -9525,16 +9131,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M26" s="12" t="inlineStr"/>
-      <c r="N26" s="27" t="inlineStr">
+      <c r="M26" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N26" s="12" t="n"/>
       <c r="O26" s="12" t="n"/>
-      <c r="P26" s="12" t="n"/>
-      <c r="Q26" s="28" t="n"/>
-      <c r="R26" s="12" t="n"/>
+      <c r="P26" s="28" t="n"/>
+      <c r="Q26" s="12" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
@@ -9597,16 +9202,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M27" s="12" t="inlineStr"/>
-      <c r="N27" s="27" t="inlineStr">
+      <c r="M27" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N27" s="12" t="n"/>
       <c r="O27" s="12" t="n"/>
-      <c r="P27" s="12" t="n"/>
-      <c r="Q27" s="28" t="n"/>
-      <c r="R27" s="12" t="n"/>
+      <c r="P27" s="28" t="n"/>
+      <c r="Q27" s="12" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
@@ -9669,16 +9273,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M28" s="12" t="inlineStr"/>
-      <c r="N28" s="27" t="inlineStr">
+      <c r="M28" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N28" s="12" t="n"/>
       <c r="O28" s="12" t="n"/>
-      <c r="P28" s="12" t="n"/>
-      <c r="Q28" s="28" t="n"/>
-      <c r="R28" s="12" t="n"/>
+      <c r="P28" s="28" t="n"/>
+      <c r="Q28" s="12" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
@@ -9742,16 +9345,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M29" s="12" t="inlineStr"/>
-      <c r="N29" s="27" t="inlineStr">
+      <c r="M29" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N29" s="12" t="n"/>
       <c r="O29" s="12" t="n"/>
-      <c r="P29" s="12" t="n"/>
-      <c r="Q29" s="28" t="n"/>
-      <c r="R29" s="12" t="n"/>
+      <c r="P29" s="28" t="n"/>
+      <c r="Q29" s="12" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
@@ -9815,16 +9417,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M30" s="12" t="inlineStr"/>
-      <c r="N30" s="27" t="inlineStr">
+      <c r="M30" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N30" s="12" t="n"/>
       <c r="O30" s="12" t="n"/>
-      <c r="P30" s="12" t="n"/>
-      <c r="Q30" s="28" t="n"/>
-      <c r="R30" s="12" t="n"/>
+      <c r="P30" s="28" t="n"/>
+      <c r="Q30" s="12" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
@@ -9888,16 +9489,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M31" s="12" t="inlineStr"/>
-      <c r="N31" s="27" t="inlineStr">
+      <c r="M31" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N31" s="12" t="n"/>
       <c r="O31" s="12" t="n"/>
-      <c r="P31" s="12" t="n"/>
-      <c r="Q31" s="28" t="n"/>
-      <c r="R31" s="12" t="n"/>
+      <c r="P31" s="28" t="n"/>
+      <c r="Q31" s="12" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
@@ -9961,16 +9561,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M32" s="12" t="inlineStr"/>
-      <c r="N32" s="27" t="inlineStr">
+      <c r="M32" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N32" s="12" t="n"/>
       <c r="O32" s="12" t="n"/>
-      <c r="P32" s="12" t="n"/>
-      <c r="Q32" s="28" t="n"/>
-      <c r="R32" s="12" t="n"/>
+      <c r="P32" s="28" t="n"/>
+      <c r="Q32" s="12" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
@@ -10033,16 +9632,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M33" s="12" t="inlineStr"/>
-      <c r="N33" s="27" t="inlineStr">
+      <c r="M33" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N33" s="12" t="n"/>
       <c r="O33" s="12" t="n"/>
-      <c r="P33" s="12" t="n"/>
-      <c r="Q33" s="28" t="n"/>
-      <c r="R33" s="12" t="n"/>
+      <c r="P33" s="28" t="n"/>
+      <c r="Q33" s="12" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
@@ -10106,16 +9704,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M34" s="12" t="inlineStr"/>
-      <c r="N34" s="27" t="inlineStr">
+      <c r="M34" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N34" s="12" t="n"/>
       <c r="O34" s="12" t="n"/>
-      <c r="P34" s="12" t="n"/>
-      <c r="Q34" s="28" t="n"/>
-      <c r="R34" s="12" t="n"/>
+      <c r="P34" s="28" t="n"/>
+      <c r="Q34" s="12" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
@@ -10179,16 +9776,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M35" s="12" t="inlineStr"/>
-      <c r="N35" s="27" t="inlineStr">
+      <c r="M35" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N35" s="12" t="n"/>
       <c r="O35" s="12" t="n"/>
-      <c r="P35" s="12" t="n"/>
-      <c r="Q35" s="28" t="n"/>
-      <c r="R35" s="12" t="n"/>
+      <c r="P35" s="28" t="n"/>
+      <c r="Q35" s="12" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
@@ -10252,16 +9848,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M36" s="12" t="inlineStr"/>
-      <c r="N36" s="27" t="inlineStr">
+      <c r="M36" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N36" s="12" t="n"/>
       <c r="O36" s="12" t="n"/>
-      <c r="P36" s="12" t="n"/>
-      <c r="Q36" s="28" t="n"/>
-      <c r="R36" s="12" t="n"/>
+      <c r="P36" s="28" t="n"/>
+      <c r="Q36" s="12" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
@@ -10324,16 +9919,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M37" s="12" t="inlineStr"/>
-      <c r="N37" s="27" t="inlineStr">
+      <c r="M37" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N37" s="12" t="n"/>
       <c r="O37" s="12" t="n"/>
-      <c r="P37" s="12" t="n"/>
-      <c r="Q37" s="28" t="n"/>
-      <c r="R37" s="12" t="n"/>
+      <c r="P37" s="28" t="n"/>
+      <c r="Q37" s="12" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
@@ -10397,16 +9991,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M38" s="12" t="inlineStr"/>
-      <c r="N38" s="27" t="inlineStr">
+      <c r="M38" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N38" s="12" t="n"/>
       <c r="O38" s="12" t="n"/>
-      <c r="P38" s="12" t="n"/>
-      <c r="Q38" s="28" t="n"/>
-      <c r="R38" s="12" t="n"/>
+      <c r="P38" s="28" t="n"/>
+      <c r="Q38" s="12" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
@@ -10469,16 +10062,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M39" s="12" t="inlineStr"/>
-      <c r="N39" s="27" t="inlineStr">
+      <c r="M39" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N39" s="12" t="n"/>
       <c r="O39" s="12" t="n"/>
-      <c r="P39" s="12" t="n"/>
-      <c r="Q39" s="28" t="n"/>
-      <c r="R39" s="12" t="n"/>
+      <c r="P39" s="28" t="n"/>
+      <c r="Q39" s="12" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
@@ -10541,16 +10133,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M40" s="12" t="inlineStr"/>
-      <c r="N40" s="27" t="inlineStr">
+      <c r="M40" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N40" s="12" t="n"/>
       <c r="O40" s="12" t="n"/>
-      <c r="P40" s="12" t="n"/>
-      <c r="Q40" s="28" t="n"/>
-      <c r="R40" s="12" t="n"/>
+      <c r="P40" s="28" t="n"/>
+      <c r="Q40" s="12" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
@@ -10600,7 +10191,7 @@
       </c>
       <c r="J41" s="12" t="inlineStr">
         <is>
-          <t>1. Look for an edit action on the policy number; call the claim update with another policy number.</t>
+          <t>1. Look for an edit action on the policy number; send a direct request to update the claim with another policy number.</t>
         </is>
       </c>
       <c r="K41" s="12" t="inlineStr">
@@ -10613,16 +10204,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M41" s="12" t="inlineStr"/>
-      <c r="N41" s="27" t="inlineStr">
+      <c r="M41" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N41" s="12" t="n"/>
       <c r="O41" s="12" t="n"/>
-      <c r="P41" s="12" t="n"/>
-      <c r="Q41" s="28" t="n"/>
-      <c r="R41" s="12" t="n"/>
+      <c r="P41" s="28" t="n"/>
+      <c r="Q41" s="12" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
@@ -10685,16 +10275,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M42" s="12" t="inlineStr"/>
-      <c r="N42" s="27" t="inlineStr">
+      <c r="M42" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N42" s="12" t="n"/>
       <c r="O42" s="12" t="n"/>
-      <c r="P42" s="12" t="n"/>
-      <c r="Q42" s="28" t="n"/>
-      <c r="R42" s="12" t="n"/>
+      <c r="P42" s="28" t="n"/>
+      <c r="Q42" s="12" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
@@ -10757,16 +10346,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M43" s="12" t="inlineStr"/>
-      <c r="N43" s="27" t="inlineStr">
+      <c r="M43" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N43" s="12" t="n"/>
       <c r="O43" s="12" t="n"/>
-      <c r="P43" s="12" t="n"/>
-      <c r="Q43" s="28" t="n"/>
-      <c r="R43" s="12" t="n"/>
+      <c r="P43" s="28" t="n"/>
+      <c r="Q43" s="12" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
@@ -10829,16 +10417,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M44" s="12" t="inlineStr"/>
-      <c r="N44" s="27" t="inlineStr">
+      <c r="M44" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N44" s="12" t="n"/>
       <c r="O44" s="12" t="n"/>
-      <c r="P44" s="12" t="n"/>
-      <c r="Q44" s="28" t="n"/>
-      <c r="R44" s="12" t="n"/>
+      <c r="P44" s="28" t="n"/>
+      <c r="Q44" s="12" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
@@ -10901,16 +10488,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M45" s="12" t="inlineStr"/>
-      <c r="N45" s="27" t="inlineStr">
+      <c r="M45" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N45" s="12" t="n"/>
       <c r="O45" s="12" t="n"/>
-      <c r="P45" s="12" t="n"/>
-      <c r="Q45" s="28" t="n"/>
-      <c r="R45" s="12" t="n"/>
+      <c r="P45" s="28" t="n"/>
+      <c r="Q45" s="12" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
@@ -10973,16 +10559,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M46" s="12" t="inlineStr"/>
-      <c r="N46" s="27" t="inlineStr">
+      <c r="M46" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N46" s="12" t="n"/>
       <c r="O46" s="12" t="n"/>
-      <c r="P46" s="12" t="n"/>
-      <c r="Q46" s="28" t="n"/>
-      <c r="R46" s="12" t="n"/>
+      <c r="P46" s="28" t="n"/>
+      <c r="Q46" s="12" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
@@ -11045,16 +10630,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M47" s="12" t="inlineStr"/>
-      <c r="N47" s="27" t="inlineStr">
+      <c r="M47" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N47" s="12" t="n"/>
       <c r="O47" s="12" t="n"/>
-      <c r="P47" s="12" t="n"/>
-      <c r="Q47" s="28" t="n"/>
-      <c r="R47" s="12" t="n"/>
+      <c r="P47" s="28" t="n"/>
+      <c r="Q47" s="12" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
@@ -11117,16 +10701,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M48" s="12" t="inlineStr"/>
-      <c r="N48" s="27" t="inlineStr">
+      <c r="M48" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N48" s="12" t="n"/>
       <c r="O48" s="12" t="n"/>
-      <c r="P48" s="12" t="n"/>
-      <c r="Q48" s="28" t="n"/>
-      <c r="R48" s="12" t="n"/>
+      <c r="P48" s="28" t="n"/>
+      <c r="Q48" s="12" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
@@ -11189,16 +10772,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M49" s="12" t="inlineStr"/>
-      <c r="N49" s="27" t="inlineStr">
+      <c r="M49" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N49" s="12" t="n"/>
       <c r="O49" s="12" t="n"/>
-      <c r="P49" s="12" t="n"/>
-      <c r="Q49" s="28" t="n"/>
-      <c r="R49" s="12" t="n"/>
+      <c r="P49" s="28" t="n"/>
+      <c r="Q49" s="12" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
@@ -11261,16 +10843,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M50" s="12" t="inlineStr"/>
-      <c r="N50" s="27" t="inlineStr">
+      <c r="M50" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N50" s="12" t="n"/>
       <c r="O50" s="12" t="n"/>
-      <c r="P50" s="12" t="n"/>
-      <c r="Q50" s="28" t="n"/>
-      <c r="R50" s="12" t="n"/>
+      <c r="P50" s="28" t="n"/>
+      <c r="Q50" s="12" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
@@ -11320,12 +10901,12 @@
       </c>
       <c r="J51" s="12" t="inlineStr">
         <is>
-          <t>1. Look at Generate Authorization Code; call the endpoint.</t>
+          <t>1. Look at Generate Authorization Code; send the request directly.</t>
         </is>
       </c>
       <c r="K51" s="12" t="inlineStr">
         <is>
-          <t>The button is disabled; the call is refused.
+          <t>The button is disabled; a direct request is refused.
 Message "The premium of ARN-2026-000602 2026 is not fully paid. The authorization code cannot be generated".</t>
         </is>
       </c>
@@ -11334,16 +10915,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M51" s="12" t="inlineStr"/>
-      <c r="N51" s="27" t="inlineStr">
+      <c r="M51" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N51" s="12" t="n"/>
       <c r="O51" s="12" t="n"/>
-      <c r="P51" s="12" t="n"/>
-      <c r="Q51" s="28" t="n"/>
-      <c r="R51" s="12" t="n"/>
+      <c r="P51" s="28" t="n"/>
+      <c r="Q51" s="12" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
@@ -11406,16 +10986,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M52" s="12" t="inlineStr"/>
-      <c r="N52" s="27" t="inlineStr">
+      <c r="M52" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N52" s="12" t="n"/>
       <c r="O52" s="12" t="n"/>
-      <c r="P52" s="12" t="n"/>
-      <c r="Q52" s="28" t="n"/>
-      <c r="R52" s="12" t="n"/>
+      <c r="P52" s="28" t="n"/>
+      <c r="Q52" s="12" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
@@ -11478,16 +11057,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M53" s="12" t="inlineStr"/>
-      <c r="N53" s="27" t="inlineStr">
+      <c r="M53" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N53" s="12" t="n"/>
       <c r="O53" s="12" t="n"/>
-      <c r="P53" s="12" t="n"/>
-      <c r="Q53" s="28" t="n"/>
-      <c r="R53" s="12" t="n"/>
+      <c r="P53" s="28" t="n"/>
+      <c r="Q53" s="12" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
@@ -11551,16 +11129,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M54" s="12" t="inlineStr"/>
-      <c r="N54" s="27" t="inlineStr">
+      <c r="M54" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N54" s="12" t="n"/>
       <c r="O54" s="12" t="n"/>
-      <c r="P54" s="12" t="n"/>
-      <c r="Q54" s="28" t="n"/>
-      <c r="R54" s="12" t="n"/>
+      <c r="P54" s="28" t="n"/>
+      <c r="Q54" s="12" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
@@ -11624,16 +11201,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M55" s="12" t="inlineStr"/>
-      <c r="N55" s="27" t="inlineStr">
+      <c r="M55" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N55" s="12" t="n"/>
       <c r="O55" s="12" t="n"/>
-      <c r="P55" s="12" t="n"/>
-      <c r="Q55" s="28" t="n"/>
-      <c r="R55" s="12" t="n"/>
+      <c r="P55" s="28" t="n"/>
+      <c r="Q55" s="12" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
@@ -11696,16 +11272,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M56" s="12" t="inlineStr"/>
-      <c r="N56" s="27" t="inlineStr">
+      <c r="M56" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N56" s="12" t="n"/>
       <c r="O56" s="12" t="n"/>
-      <c r="P56" s="12" t="n"/>
-      <c r="Q56" s="28" t="n"/>
-      <c r="R56" s="12" t="n"/>
+      <c r="P56" s="28" t="n"/>
+      <c r="Q56" s="12" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
@@ -11768,16 +11343,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M57" s="12" t="inlineStr"/>
-      <c r="N57" s="27" t="inlineStr">
+      <c r="M57" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N57" s="12" t="n"/>
       <c r="O57" s="12" t="n"/>
-      <c r="P57" s="12" t="n"/>
-      <c r="Q57" s="28" t="n"/>
-      <c r="R57" s="12" t="n"/>
+      <c r="P57" s="28" t="n"/>
+      <c r="Q57" s="12" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
@@ -11817,7 +11391,7 @@
       </c>
       <c r="H58" s="12" t="inlineStr">
         <is>
-          <t>API call with the user's token (tester tool, for example Postman)</t>
+          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I58" s="12" t="inlineStr">
@@ -11827,7 +11401,7 @@
       </c>
       <c r="J58" s="12" t="inlineStr">
         <is>
-          <t>1. Call the link endpoint with a location item of ARN-2026-000501.</t>
+          <t>1. Send a direct request to link a location item of ARN-2026-000501.</t>
         </is>
       </c>
       <c r="K58" s="12" t="inlineStr">
@@ -11841,16 +11415,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M58" s="12" t="inlineStr"/>
-      <c r="N58" s="27" t="inlineStr">
+      <c r="M58" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N58" s="12" t="n"/>
       <c r="O58" s="12" t="n"/>
-      <c r="P58" s="12" t="n"/>
-      <c r="Q58" s="28" t="n"/>
-      <c r="R58" s="12" t="n"/>
+      <c r="P58" s="28" t="n"/>
+      <c r="Q58" s="12" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
@@ -11914,16 +11487,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M59" s="12" t="inlineStr"/>
-      <c r="N59" s="27" t="inlineStr">
+      <c r="M59" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N59" s="12" t="n"/>
       <c r="O59" s="12" t="n"/>
-      <c r="P59" s="12" t="n"/>
-      <c r="Q59" s="28" t="n"/>
-      <c r="R59" s="12" t="n"/>
+      <c r="P59" s="28" t="n"/>
+      <c r="Q59" s="12" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="12" t="inlineStr">
@@ -11986,16 +11558,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M60" s="12" t="inlineStr"/>
-      <c r="N60" s="27" t="inlineStr">
+      <c r="M60" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N60" s="12" t="n"/>
       <c r="O60" s="12" t="n"/>
-      <c r="P60" s="12" t="n"/>
-      <c r="Q60" s="28" t="n"/>
-      <c r="R60" s="12" t="n"/>
+      <c r="P60" s="28" t="n"/>
+      <c r="Q60" s="12" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="12" t="inlineStr">
@@ -12058,16 +11629,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M61" s="12" t="inlineStr"/>
-      <c r="N61" s="27" t="inlineStr">
+      <c r="M61" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N61" s="12" t="n"/>
       <c r="O61" s="12" t="n"/>
-      <c r="P61" s="12" t="n"/>
-      <c r="Q61" s="28" t="n"/>
-      <c r="R61" s="12" t="n"/>
+      <c r="P61" s="28" t="n"/>
+      <c r="Q61" s="12" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
@@ -12130,16 +11700,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M62" s="12" t="inlineStr"/>
-      <c r="N62" s="27" t="inlineStr">
+      <c r="M62" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N62" s="12" t="n"/>
       <c r="O62" s="12" t="n"/>
-      <c r="P62" s="12" t="n"/>
-      <c r="Q62" s="28" t="n"/>
-      <c r="R62" s="12" t="n"/>
+      <c r="P62" s="28" t="n"/>
+      <c r="Q62" s="12" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="12" t="inlineStr">
@@ -12203,16 +11772,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M63" s="12" t="inlineStr"/>
-      <c r="N63" s="27" t="inlineStr">
+      <c r="M63" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N63" s="12" t="n"/>
       <c r="O63" s="12" t="n"/>
-      <c r="P63" s="12" t="n"/>
-      <c r="Q63" s="28" t="n"/>
-      <c r="R63" s="12" t="n"/>
+      <c r="P63" s="28" t="n"/>
+      <c r="Q63" s="12" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="12" t="inlineStr">
@@ -12275,16 +11843,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M64" s="12" t="inlineStr"/>
-      <c r="N64" s="27" t="inlineStr">
+      <c r="M64" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N64" s="12" t="n"/>
       <c r="O64" s="12" t="n"/>
-      <c r="P64" s="12" t="n"/>
-      <c r="Q64" s="28" t="n"/>
-      <c r="R64" s="12" t="n"/>
+      <c r="P64" s="28" t="n"/>
+      <c r="Q64" s="12" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
@@ -12348,16 +11915,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M65" s="12" t="inlineStr"/>
-      <c r="N65" s="27" t="inlineStr">
+      <c r="M65" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N65" s="12" t="n"/>
       <c r="O65" s="12" t="n"/>
-      <c r="P65" s="12" t="n"/>
-      <c r="Q65" s="28" t="n"/>
-      <c r="R65" s="12" t="n"/>
+      <c r="P65" s="28" t="n"/>
+      <c r="Q65" s="12" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="12" t="inlineStr">
@@ -12420,16 +11986,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M66" s="12" t="inlineStr"/>
-      <c r="N66" s="27" t="inlineStr">
+      <c r="M66" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N66" s="12" t="n"/>
       <c r="O66" s="12" t="n"/>
-      <c r="P66" s="12" t="n"/>
-      <c r="Q66" s="28" t="n"/>
-      <c r="R66" s="12" t="n"/>
+      <c r="P66" s="28" t="n"/>
+      <c r="Q66" s="12" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="12" t="inlineStr">
@@ -12492,16 +12057,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M67" s="12" t="inlineStr"/>
-      <c r="N67" s="27" t="inlineStr">
+      <c r="M67" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N67" s="12" t="n"/>
       <c r="O67" s="12" t="n"/>
-      <c r="P67" s="12" t="n"/>
-      <c r="Q67" s="28" t="n"/>
-      <c r="R67" s="12" t="n"/>
+      <c r="P67" s="28" t="n"/>
+      <c r="Q67" s="12" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="12" t="inlineStr">
@@ -12564,16 +12128,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M68" s="12" t="inlineStr"/>
-      <c r="N68" s="27" t="inlineStr">
+      <c r="M68" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N68" s="12" t="n"/>
       <c r="O68" s="12" t="n"/>
-      <c r="P68" s="12" t="n"/>
-      <c r="Q68" s="28" t="n"/>
-      <c r="R68" s="12" t="n"/>
+      <c r="P68" s="28" t="n"/>
+      <c r="Q68" s="12" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="12" t="inlineStr">
@@ -12636,16 +12199,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M69" s="12" t="inlineStr"/>
-      <c r="N69" s="27" t="inlineStr">
+      <c r="M69" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N69" s="12" t="n"/>
       <c r="O69" s="12" t="n"/>
-      <c r="P69" s="12" t="n"/>
-      <c r="Q69" s="28" t="n"/>
-      <c r="R69" s="12" t="n"/>
+      <c r="P69" s="28" t="n"/>
+      <c r="Q69" s="12" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="12" t="inlineStr">
@@ -12709,16 +12271,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M70" s="12" t="inlineStr"/>
-      <c r="N70" s="27" t="inlineStr">
+      <c r="M70" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N70" s="12" t="n"/>
       <c r="O70" s="12" t="n"/>
-      <c r="P70" s="12" t="n"/>
-      <c r="Q70" s="28" t="n"/>
-      <c r="R70" s="12" t="n"/>
+      <c r="P70" s="28" t="n"/>
+      <c r="Q70" s="12" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="12" t="inlineStr">
@@ -12781,16 +12342,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M71" s="12" t="inlineStr"/>
-      <c r="N71" s="27" t="inlineStr">
+      <c r="M71" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N71" s="12" t="n"/>
       <c r="O71" s="12" t="n"/>
-      <c r="P71" s="12" t="n"/>
-      <c r="Q71" s="28" t="n"/>
-      <c r="R71" s="12" t="n"/>
+      <c r="P71" s="28" t="n"/>
+      <c r="Q71" s="12" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="12" t="inlineStr">
@@ -12854,16 +12414,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M72" s="12" t="inlineStr"/>
-      <c r="N72" s="27" t="inlineStr">
+      <c r="M72" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N72" s="12" t="n"/>
       <c r="O72" s="12" t="n"/>
-      <c r="P72" s="12" t="n"/>
-      <c r="Q72" s="28" t="n"/>
-      <c r="R72" s="12" t="n"/>
+      <c r="P72" s="28" t="n"/>
+      <c r="Q72" s="12" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="12" t="inlineStr">
@@ -12926,16 +12485,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M73" s="12" t="inlineStr"/>
-      <c r="N73" s="27" t="inlineStr">
+      <c r="M73" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N73" s="12" t="n"/>
       <c r="O73" s="12" t="n"/>
-      <c r="P73" s="12" t="n"/>
-      <c r="Q73" s="28" t="n"/>
-      <c r="R73" s="12" t="n"/>
+      <c r="P73" s="28" t="n"/>
+      <c r="Q73" s="12" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="12" t="inlineStr">
@@ -12998,16 +12556,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M74" s="12" t="inlineStr"/>
-      <c r="N74" s="27" t="inlineStr">
+      <c r="M74" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N74" s="12" t="n"/>
       <c r="O74" s="12" t="n"/>
-      <c r="P74" s="12" t="n"/>
-      <c r="Q74" s="28" t="n"/>
-      <c r="R74" s="12" t="n"/>
+      <c r="P74" s="28" t="n"/>
+      <c r="Q74" s="12" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="12" t="inlineStr">
@@ -13071,16 +12628,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M75" s="12" t="inlineStr"/>
-      <c r="N75" s="27" t="inlineStr">
+      <c r="M75" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N75" s="12" t="n"/>
       <c r="O75" s="12" t="n"/>
-      <c r="P75" s="12" t="n"/>
-      <c r="Q75" s="28" t="n"/>
-      <c r="R75" s="12" t="n"/>
+      <c r="P75" s="28" t="n"/>
+      <c r="Q75" s="12" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="12" t="inlineStr">
@@ -13144,16 +12700,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M76" s="12" t="inlineStr"/>
-      <c r="N76" s="27" t="inlineStr">
+      <c r="M76" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N76" s="12" t="n"/>
       <c r="O76" s="12" t="n"/>
-      <c r="P76" s="12" t="n"/>
-      <c r="Q76" s="28" t="n"/>
-      <c r="R76" s="12" t="n"/>
+      <c r="P76" s="28" t="n"/>
+      <c r="Q76" s="12" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="12" t="inlineStr">
@@ -13216,16 +12771,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M77" s="12" t="inlineStr"/>
-      <c r="N77" s="27" t="inlineStr">
+      <c r="M77" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N77" s="12" t="n"/>
       <c r="O77" s="12" t="n"/>
-      <c r="P77" s="12" t="n"/>
-      <c r="Q77" s="28" t="n"/>
-      <c r="R77" s="12" t="n"/>
+      <c r="P77" s="28" t="n"/>
+      <c r="Q77" s="12" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="12" t="inlineStr">
@@ -13289,16 +12843,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M78" s="12" t="inlineStr"/>
-      <c r="N78" s="27" t="inlineStr">
+      <c r="M78" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N78" s="12" t="n"/>
       <c r="O78" s="12" t="n"/>
-      <c r="P78" s="12" t="n"/>
-      <c r="Q78" s="28" t="n"/>
-      <c r="R78" s="12" t="n"/>
+      <c r="P78" s="28" t="n"/>
+      <c r="Q78" s="12" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="12" t="inlineStr">
@@ -13361,16 +12914,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M79" s="12" t="inlineStr"/>
-      <c r="N79" s="27" t="inlineStr">
+      <c r="M79" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N79" s="12" t="n"/>
       <c r="O79" s="12" t="n"/>
-      <c r="P79" s="12" t="n"/>
-      <c r="Q79" s="28" t="n"/>
-      <c r="R79" s="12" t="n"/>
+      <c r="P79" s="28" t="n"/>
+      <c r="Q79" s="12" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="12" t="inlineStr">
@@ -13434,16 +12986,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M80" s="12" t="inlineStr"/>
-      <c r="N80" s="27" t="inlineStr">
+      <c r="M80" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N80" s="12" t="n"/>
       <c r="O80" s="12" t="n"/>
-      <c r="P80" s="12" t="n"/>
-      <c r="Q80" s="28" t="n"/>
-      <c r="R80" s="12" t="n"/>
+      <c r="P80" s="28" t="n"/>
+      <c r="Q80" s="12" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="12" t="inlineStr">
@@ -13507,16 +13058,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M81" s="12" t="inlineStr"/>
-      <c r="N81" s="27" t="inlineStr">
+      <c r="M81" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N81" s="12" t="n"/>
       <c r="O81" s="12" t="n"/>
-      <c r="P81" s="12" t="n"/>
-      <c r="Q81" s="28" t="n"/>
-      <c r="R81" s="12" t="n"/>
+      <c r="P81" s="28" t="n"/>
+      <c r="Q81" s="12" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="12" t="inlineStr">
@@ -13580,16 +13130,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M82" s="12" t="inlineStr"/>
-      <c r="N82" s="27" t="inlineStr">
+      <c r="M82" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N82" s="12" t="n"/>
       <c r="O82" s="12" t="n"/>
-      <c r="P82" s="12" t="n"/>
-      <c r="Q82" s="28" t="n"/>
-      <c r="R82" s="12" t="n"/>
+      <c r="P82" s="28" t="n"/>
+      <c r="Q82" s="12" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="12" t="inlineStr">
@@ -13652,16 +13201,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M83" s="12" t="inlineStr"/>
-      <c r="N83" s="27" t="inlineStr">
+      <c r="M83" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N83" s="12" t="n"/>
       <c r="O83" s="12" t="n"/>
-      <c r="P83" s="12" t="n"/>
-      <c r="Q83" s="28" t="n"/>
-      <c r="R83" s="12" t="n"/>
+      <c r="P83" s="28" t="n"/>
+      <c r="Q83" s="12" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="12" t="inlineStr">
@@ -13724,16 +13272,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M84" s="12" t="inlineStr"/>
-      <c r="N84" s="27" t="inlineStr">
+      <c r="M84" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N84" s="12" t="n"/>
       <c r="O84" s="12" t="n"/>
-      <c r="P84" s="12" t="n"/>
-      <c r="Q84" s="28" t="n"/>
-      <c r="R84" s="12" t="n"/>
+      <c r="P84" s="28" t="n"/>
+      <c r="Q84" s="12" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="12" t="inlineStr">
@@ -13797,16 +13344,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M85" s="12" t="inlineStr"/>
-      <c r="N85" s="27" t="inlineStr">
+      <c r="M85" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N85" s="12" t="n"/>
       <c r="O85" s="12" t="n"/>
-      <c r="P85" s="12" t="n"/>
-      <c r="Q85" s="28" t="n"/>
-      <c r="R85" s="12" t="n"/>
+      <c r="P85" s="28" t="n"/>
+      <c r="Q85" s="12" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="12" t="inlineStr">
@@ -13869,16 +13415,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M86" s="12" t="inlineStr"/>
-      <c r="N86" s="27" t="inlineStr">
+      <c r="M86" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N86" s="12" t="n"/>
       <c r="O86" s="12" t="n"/>
-      <c r="P86" s="12" t="n"/>
-      <c r="Q86" s="28" t="n"/>
-      <c r="R86" s="12" t="n"/>
+      <c r="P86" s="28" t="n"/>
+      <c r="Q86" s="12" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="12" t="inlineStr">
@@ -13941,16 +13486,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M87" s="12" t="inlineStr"/>
-      <c r="N87" s="27" t="inlineStr">
+      <c r="M87" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N87" s="12" t="n"/>
       <c r="O87" s="12" t="n"/>
-      <c r="P87" s="12" t="n"/>
-      <c r="Q87" s="28" t="n"/>
-      <c r="R87" s="12" t="n"/>
+      <c r="P87" s="28" t="n"/>
+      <c r="Q87" s="12" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="12" t="inlineStr">
@@ -14013,16 +13557,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M88" s="12" t="inlineStr"/>
-      <c r="N88" s="27" t="inlineStr">
+      <c r="M88" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N88" s="12" t="n"/>
       <c r="O88" s="12" t="n"/>
-      <c r="P88" s="12" t="n"/>
-      <c r="Q88" s="28" t="n"/>
-      <c r="R88" s="12" t="n"/>
+      <c r="P88" s="28" t="n"/>
+      <c r="Q88" s="12" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="12" t="inlineStr">
@@ -14085,16 +13628,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M89" s="12" t="inlineStr"/>
-      <c r="N89" s="27" t="inlineStr">
+      <c r="M89" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N89" s="12" t="n"/>
       <c r="O89" s="12" t="n"/>
-      <c r="P89" s="12" t="n"/>
-      <c r="Q89" s="28" t="n"/>
-      <c r="R89" s="12" t="n"/>
+      <c r="P89" s="28" t="n"/>
+      <c r="Q89" s="12" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="12" t="inlineStr">
@@ -14157,16 +13699,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M90" s="12" t="inlineStr"/>
-      <c r="N90" s="27" t="inlineStr">
+      <c r="M90" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N90" s="12" t="n"/>
       <c r="O90" s="12" t="n"/>
-      <c r="P90" s="12" t="n"/>
-      <c r="Q90" s="28" t="n"/>
-      <c r="R90" s="12" t="n"/>
+      <c r="P90" s="28" t="n"/>
+      <c r="Q90" s="12" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="12" t="inlineStr">
@@ -14230,16 +13771,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M91" s="12" t="inlineStr"/>
-      <c r="N91" s="27" t="inlineStr">
+      <c r="M91" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N91" s="12" t="n"/>
       <c r="O91" s="12" t="n"/>
-      <c r="P91" s="12" t="n"/>
-      <c r="Q91" s="28" t="n"/>
-      <c r="R91" s="12" t="n"/>
+      <c r="P91" s="28" t="n"/>
+      <c r="Q91" s="12" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="12" t="inlineStr">
@@ -14289,12 +13829,12 @@
       </c>
       <c r="J92" s="12" t="inlineStr">
         <is>
-          <t>1. As cl.officer1 open the claim; call the endpoint.</t>
+          <t>1. As cl.officer1 open the claim; send the request directly.</t>
         </is>
       </c>
       <c r="K92" s="12" t="inlineStr">
         <is>
-          <t>The action is not shown; the call returns HTTP 403.
+          <t>The action is not shown; the request is refused.
 Message "You are not permitted to perform this action".</t>
         </is>
       </c>
@@ -14303,16 +13843,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M92" s="12" t="inlineStr"/>
-      <c r="N92" s="27" t="inlineStr">
+      <c r="M92" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N92" s="12" t="n"/>
       <c r="O92" s="12" t="n"/>
-      <c r="P92" s="12" t="n"/>
-      <c r="Q92" s="28" t="n"/>
-      <c r="R92" s="12" t="n"/>
+      <c r="P92" s="28" t="n"/>
+      <c r="Q92" s="12" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="12" t="inlineStr">
@@ -14375,16 +13914,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M93" s="12" t="inlineStr"/>
-      <c r="N93" s="27" t="inlineStr">
+      <c r="M93" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N93" s="12" t="n"/>
       <c r="O93" s="12" t="n"/>
-      <c r="P93" s="12" t="n"/>
-      <c r="Q93" s="28" t="n"/>
-      <c r="R93" s="12" t="n"/>
+      <c r="P93" s="28" t="n"/>
+      <c r="Q93" s="12" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="12" t="inlineStr">
@@ -14447,16 +13985,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M94" s="12" t="inlineStr"/>
-      <c r="N94" s="27" t="inlineStr">
+      <c r="M94" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N94" s="12" t="n"/>
       <c r="O94" s="12" t="n"/>
-      <c r="P94" s="12" t="n"/>
-      <c r="Q94" s="28" t="n"/>
-      <c r="R94" s="12" t="n"/>
+      <c r="P94" s="28" t="n"/>
+      <c r="Q94" s="12" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="12" t="inlineStr">
@@ -14519,16 +14056,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M95" s="12" t="inlineStr"/>
-      <c r="N95" s="27" t="inlineStr">
+      <c r="M95" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N95" s="12" t="n"/>
       <c r="O95" s="12" t="n"/>
-      <c r="P95" s="12" t="n"/>
-      <c r="Q95" s="28" t="n"/>
-      <c r="R95" s="12" t="n"/>
+      <c r="P95" s="28" t="n"/>
+      <c r="Q95" s="12" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="12" t="inlineStr">
@@ -14592,16 +14128,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M96" s="12" t="inlineStr"/>
-      <c r="N96" s="27" t="inlineStr">
+      <c r="M96" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N96" s="12" t="n"/>
       <c r="O96" s="12" t="n"/>
-      <c r="P96" s="12" t="n"/>
-      <c r="Q96" s="28" t="n"/>
-      <c r="R96" s="12" t="n"/>
+      <c r="P96" s="28" t="n"/>
+      <c r="Q96" s="12" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="12" t="inlineStr">
@@ -14664,16 +14199,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M97" s="12" t="inlineStr"/>
-      <c r="N97" s="27" t="inlineStr">
+      <c r="M97" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N97" s="12" t="n"/>
       <c r="O97" s="12" t="n"/>
-      <c r="P97" s="12" t="n"/>
-      <c r="Q97" s="28" t="n"/>
-      <c r="R97" s="12" t="n"/>
+      <c r="P97" s="28" t="n"/>
+      <c r="Q97" s="12" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="12" t="inlineStr">
@@ -14736,16 +14270,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M98" s="12" t="inlineStr"/>
-      <c r="N98" s="27" t="inlineStr">
+      <c r="M98" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N98" s="12" t="n"/>
       <c r="O98" s="12" t="n"/>
-      <c r="P98" s="12" t="n"/>
-      <c r="Q98" s="28" t="n"/>
-      <c r="R98" s="12" t="n"/>
+      <c r="P98" s="28" t="n"/>
+      <c r="Q98" s="12" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="12" t="inlineStr">
@@ -14808,16 +14341,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M99" s="12" t="inlineStr"/>
-      <c r="N99" s="27" t="inlineStr">
+      <c r="M99" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N99" s="12" t="n"/>
       <c r="O99" s="12" t="n"/>
-      <c r="P99" s="12" t="n"/>
-      <c r="Q99" s="28" t="n"/>
-      <c r="R99" s="12" t="n"/>
+      <c r="P99" s="28" t="n"/>
+      <c r="Q99" s="12" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="12" t="inlineStr">
@@ -14880,16 +14412,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M100" s="12" t="inlineStr"/>
-      <c r="N100" s="27" t="inlineStr">
+      <c r="M100" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N100" s="12" t="n"/>
       <c r="O100" s="12" t="n"/>
-      <c r="P100" s="12" t="n"/>
-      <c r="Q100" s="28" t="n"/>
-      <c r="R100" s="12" t="n"/>
+      <c r="P100" s="28" t="n"/>
+      <c r="Q100" s="12" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="12" t="inlineStr">
@@ -14953,16 +14484,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M101" s="12" t="inlineStr"/>
-      <c r="N101" s="27" t="inlineStr">
+      <c r="M101" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N101" s="12" t="n"/>
       <c r="O101" s="12" t="n"/>
-      <c r="P101" s="12" t="n"/>
-      <c r="Q101" s="28" t="n"/>
-      <c r="R101" s="12" t="n"/>
+      <c r="P101" s="28" t="n"/>
+      <c r="Q101" s="12" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="12" t="inlineStr">
@@ -15025,16 +14555,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M102" s="12" t="inlineStr"/>
-      <c r="N102" s="27" t="inlineStr">
+      <c r="M102" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N102" s="12" t="n"/>
       <c r="O102" s="12" t="n"/>
-      <c r="P102" s="12" t="n"/>
-      <c r="Q102" s="28" t="n"/>
-      <c r="R102" s="12" t="n"/>
+      <c r="P102" s="28" t="n"/>
+      <c r="Q102" s="12" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="12" t="inlineStr">
@@ -15099,16 +14628,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M103" s="12" t="inlineStr"/>
-      <c r="N103" s="27" t="inlineStr">
+      <c r="M103" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N103" s="12" t="n"/>
       <c r="O103" s="12" t="n"/>
-      <c r="P103" s="12" t="n"/>
-      <c r="Q103" s="28" t="n"/>
-      <c r="R103" s="12" t="n"/>
+      <c r="P103" s="28" t="n"/>
+      <c r="Q103" s="12" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="12" t="inlineStr">
@@ -15171,16 +14699,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M104" s="12" t="inlineStr"/>
-      <c r="N104" s="27" t="inlineStr">
+      <c r="M104" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N104" s="12" t="n"/>
       <c r="O104" s="12" t="n"/>
-      <c r="P104" s="12" t="n"/>
-      <c r="Q104" s="28" t="n"/>
-      <c r="R104" s="12" t="n"/>
+      <c r="P104" s="28" t="n"/>
+      <c r="Q104" s="12" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="12" t="inlineStr">
@@ -15244,16 +14771,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M105" s="12" t="inlineStr"/>
-      <c r="N105" s="27" t="inlineStr">
+      <c r="M105" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N105" s="12" t="n"/>
       <c r="O105" s="12" t="n"/>
-      <c r="P105" s="12" t="n"/>
-      <c r="Q105" s="28" t="n"/>
-      <c r="R105" s="12" t="n"/>
+      <c r="P105" s="28" t="n"/>
+      <c r="Q105" s="12" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="12" t="inlineStr">
@@ -15316,16 +14842,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M106" s="12" t="inlineStr"/>
-      <c r="N106" s="27" t="inlineStr">
+      <c r="M106" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N106" s="12" t="n"/>
       <c r="O106" s="12" t="n"/>
-      <c r="P106" s="12" t="n"/>
-      <c r="Q106" s="28" t="n"/>
-      <c r="R106" s="12" t="n"/>
+      <c r="P106" s="28" t="n"/>
+      <c r="Q106" s="12" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="12" t="inlineStr">
@@ -15350,7 +14875,7 @@
       </c>
       <c r="E107" s="12" t="inlineStr">
         <is>
-          <t>Direct call with a status outside the matrix</t>
+          <t>Direct request with a status outside the matrix</t>
         </is>
       </c>
       <c r="F107" s="12" t="inlineStr">
@@ -15365,7 +14890,7 @@
       </c>
       <c r="H107" s="12" t="inlineStr">
         <is>
-          <t>API call with the user's token (tester tool, for example Postman)</t>
+          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I107" s="12" t="inlineStr">
@@ -15375,12 +14900,12 @@
       </c>
       <c r="J107" s="12" t="inlineStr">
         <is>
-          <t>1. With cl.officer1's token set status 6 on BCL-2026-000101.</t>
+          <t>1. Signed in as cl.officer1, set status 6 on BCL-2026-000101.</t>
         </is>
       </c>
       <c r="K107" s="12" t="inlineStr">
         <is>
-          <t>The call is refused; the status is unchanged.
+          <t>The request is refused; the status is unchanged.
 Message "You are not allowed to set the status For Insurer's Issuance of Check".</t>
         </is>
       </c>
@@ -15389,16 +14914,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M107" s="12" t="inlineStr"/>
-      <c r="N107" s="27" t="inlineStr">
+      <c r="M107" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N107" s="12" t="n"/>
       <c r="O107" s="12" t="n"/>
-      <c r="P107" s="12" t="n"/>
-      <c r="Q107" s="28" t="n"/>
-      <c r="R107" s="12" t="n"/>
+      <c r="P107" s="28" t="n"/>
+      <c r="Q107" s="12" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="12" t="inlineStr">
@@ -15461,16 +14985,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M108" s="12" t="inlineStr"/>
-      <c r="N108" s="27" t="inlineStr">
+      <c r="M108" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N108" s="12" t="n"/>
       <c r="O108" s="12" t="n"/>
-      <c r="P108" s="12" t="n"/>
-      <c r="Q108" s="28" t="n"/>
-      <c r="R108" s="12" t="n"/>
+      <c r="P108" s="28" t="n"/>
+      <c r="Q108" s="12" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="12" t="inlineStr">
@@ -15534,16 +15057,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M109" s="12" t="inlineStr"/>
-      <c r="N109" s="27" t="inlineStr">
+      <c r="M109" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N109" s="12" t="n"/>
       <c r="O109" s="12" t="n"/>
-      <c r="P109" s="12" t="n"/>
-      <c r="Q109" s="28" t="n"/>
-      <c r="R109" s="12" t="n"/>
+      <c r="P109" s="28" t="n"/>
+      <c r="Q109" s="12" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="12" t="inlineStr">
@@ -15606,16 +15128,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M110" s="12" t="inlineStr"/>
-      <c r="N110" s="27" t="inlineStr">
+      <c r="M110" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N110" s="12" t="n"/>
       <c r="O110" s="12" t="n"/>
-      <c r="P110" s="12" t="n"/>
-      <c r="Q110" s="28" t="n"/>
-      <c r="R110" s="12" t="n"/>
+      <c r="P110" s="28" t="n"/>
+      <c r="Q110" s="12" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="12" t="inlineStr">
@@ -15678,16 +15199,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M111" s="12" t="inlineStr"/>
-      <c r="N111" s="27" t="inlineStr">
+      <c r="M111" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N111" s="12" t="n"/>
       <c r="O111" s="12" t="n"/>
-      <c r="P111" s="12" t="n"/>
-      <c r="Q111" s="28" t="n"/>
-      <c r="R111" s="12" t="n"/>
+      <c r="P111" s="28" t="n"/>
+      <c r="Q111" s="12" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="12" t="inlineStr">
@@ -15742,7 +15262,7 @@
       </c>
       <c r="K112" s="12" t="inlineStr">
         <is>
-          <t>The action is not offered; the call is refused.
+          <t>The action is not offered; a direct request is refused.
 Message "Claim BCL-2026-000105 is closed. Reopen it before changing the status".</t>
         </is>
       </c>
@@ -15751,16 +15271,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M112" s="12" t="inlineStr"/>
-      <c r="N112" s="27" t="inlineStr">
+      <c r="M112" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N112" s="12" t="n"/>
       <c r="O112" s="12" t="n"/>
-      <c r="P112" s="12" t="n"/>
-      <c r="Q112" s="28" t="n"/>
-      <c r="R112" s="12" t="n"/>
+      <c r="P112" s="28" t="n"/>
+      <c r="Q112" s="12" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="12" t="inlineStr">
@@ -15824,16 +15343,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M113" s="12" t="inlineStr"/>
-      <c r="N113" s="27" t="inlineStr">
+      <c r="M113" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N113" s="12" t="n"/>
       <c r="O113" s="12" t="n"/>
-      <c r="P113" s="12" t="n"/>
-      <c r="Q113" s="28" t="n"/>
-      <c r="R113" s="12" t="n"/>
+      <c r="P113" s="28" t="n"/>
+      <c r="Q113" s="12" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="12" t="inlineStr">
@@ -15896,16 +15414,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M114" s="12" t="inlineStr"/>
-      <c r="N114" s="27" t="inlineStr">
+      <c r="M114" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N114" s="12" t="n"/>
       <c r="O114" s="12" t="n"/>
-      <c r="P114" s="12" t="n"/>
-      <c r="Q114" s="28" t="n"/>
-      <c r="R114" s="12" t="n"/>
+      <c r="P114" s="28" t="n"/>
+      <c r="Q114" s="12" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="12" t="inlineStr">
@@ -15968,16 +15485,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M115" s="12" t="inlineStr"/>
-      <c r="N115" s="27" t="inlineStr">
+      <c r="M115" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N115" s="12" t="n"/>
       <c r="O115" s="12" t="n"/>
-      <c r="P115" s="12" t="n"/>
-      <c r="Q115" s="28" t="n"/>
-      <c r="R115" s="12" t="n"/>
+      <c r="P115" s="28" t="n"/>
+      <c r="Q115" s="12" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="12" t="inlineStr">
@@ -16040,16 +15556,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M116" s="12" t="inlineStr"/>
-      <c r="N116" s="27" t="inlineStr">
+      <c r="M116" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N116" s="12" t="n"/>
       <c r="O116" s="12" t="n"/>
-      <c r="P116" s="12" t="n"/>
-      <c r="Q116" s="28" t="n"/>
-      <c r="R116" s="12" t="n"/>
+      <c r="P116" s="28" t="n"/>
+      <c r="Q116" s="12" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="12" t="inlineStr">
@@ -16113,16 +15628,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M117" s="12" t="inlineStr"/>
-      <c r="N117" s="27" t="inlineStr">
+      <c r="M117" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N117" s="12" t="n"/>
       <c r="O117" s="12" t="n"/>
-      <c r="P117" s="12" t="n"/>
-      <c r="Q117" s="28" t="n"/>
-      <c r="R117" s="12" t="n"/>
+      <c r="P117" s="28" t="n"/>
+      <c r="Q117" s="12" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="12" t="inlineStr">
@@ -16186,16 +15700,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M118" s="12" t="inlineStr"/>
-      <c r="N118" s="27" t="inlineStr">
+      <c r="M118" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N118" s="12" t="n"/>
       <c r="O118" s="12" t="n"/>
-      <c r="P118" s="12" t="n"/>
-      <c r="Q118" s="28" t="n"/>
-      <c r="R118" s="12" t="n"/>
+      <c r="P118" s="28" t="n"/>
+      <c r="Q118" s="12" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="12" t="inlineStr">
@@ -16258,16 +15771,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M119" s="12" t="inlineStr"/>
-      <c r="N119" s="27" t="inlineStr">
+      <c r="M119" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N119" s="12" t="n"/>
       <c r="O119" s="12" t="n"/>
-      <c r="P119" s="12" t="n"/>
-      <c r="Q119" s="28" t="n"/>
-      <c r="R119" s="12" t="n"/>
+      <c r="P119" s="28" t="n"/>
+      <c r="Q119" s="12" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="12" t="inlineStr">
@@ -16331,16 +15843,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M120" s="12" t="inlineStr"/>
-      <c r="N120" s="27" t="inlineStr">
+      <c r="M120" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N120" s="12" t="n"/>
       <c r="O120" s="12" t="n"/>
-      <c r="P120" s="12" t="n"/>
-      <c r="Q120" s="28" t="n"/>
-      <c r="R120" s="12" t="n"/>
+      <c r="P120" s="28" t="n"/>
+      <c r="Q120" s="12" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="12" t="inlineStr">
@@ -16404,16 +15915,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M121" s="12" t="inlineStr"/>
-      <c r="N121" s="27" t="inlineStr">
+      <c r="M121" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N121" s="12" t="n"/>
       <c r="O121" s="12" t="n"/>
-      <c r="P121" s="12" t="n"/>
-      <c r="Q121" s="28" t="n"/>
-      <c r="R121" s="12" t="n"/>
+      <c r="P121" s="28" t="n"/>
+      <c r="Q121" s="12" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="12" t="inlineStr">
@@ -16478,16 +15988,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M122" s="12" t="inlineStr"/>
-      <c r="N122" s="27" t="inlineStr">
+      <c r="M122" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N122" s="12" t="n"/>
       <c r="O122" s="12" t="n"/>
-      <c r="P122" s="12" t="n"/>
-      <c r="Q122" s="28" t="n"/>
-      <c r="R122" s="12" t="n"/>
+      <c r="P122" s="28" t="n"/>
+      <c r="Q122" s="12" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="12" t="inlineStr">
@@ -16550,16 +16059,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M123" s="12" t="inlineStr"/>
-      <c r="N123" s="27" t="inlineStr">
+      <c r="M123" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N123" s="12" t="n"/>
       <c r="O123" s="12" t="n"/>
-      <c r="P123" s="12" t="n"/>
-      <c r="Q123" s="28" t="n"/>
-      <c r="R123" s="12" t="n"/>
+      <c r="P123" s="28" t="n"/>
+      <c r="Q123" s="12" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="12" t="inlineStr">
@@ -16622,16 +16130,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M124" s="12" t="inlineStr"/>
-      <c r="N124" s="27" t="inlineStr">
+      <c r="M124" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N124" s="12" t="n"/>
       <c r="O124" s="12" t="n"/>
-      <c r="P124" s="12" t="n"/>
-      <c r="Q124" s="28" t="n"/>
-      <c r="R124" s="12" t="n"/>
+      <c r="P124" s="28" t="n"/>
+      <c r="Q124" s="12" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="12" t="inlineStr">
@@ -16694,16 +16201,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M125" s="12" t="inlineStr"/>
-      <c r="N125" s="27" t="inlineStr">
+      <c r="M125" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N125" s="12" t="n"/>
       <c r="O125" s="12" t="n"/>
-      <c r="P125" s="12" t="n"/>
-      <c r="Q125" s="28" t="n"/>
-      <c r="R125" s="12" t="n"/>
+      <c r="P125" s="28" t="n"/>
+      <c r="Q125" s="12" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="12" t="inlineStr">
@@ -16766,16 +16272,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M126" s="12" t="inlineStr"/>
-      <c r="N126" s="27" t="inlineStr">
+      <c r="M126" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N126" s="12" t="n"/>
       <c r="O126" s="12" t="n"/>
-      <c r="P126" s="12" t="n"/>
-      <c r="Q126" s="28" t="n"/>
-      <c r="R126" s="12" t="n"/>
+      <c r="P126" s="28" t="n"/>
+      <c r="Q126" s="12" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="12" t="inlineStr">
@@ -16839,16 +16344,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M127" s="12" t="inlineStr"/>
-      <c r="N127" s="27" t="inlineStr">
+      <c r="M127" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N127" s="12" t="n"/>
       <c r="O127" s="12" t="n"/>
-      <c r="P127" s="12" t="n"/>
-      <c r="Q127" s="28" t="n"/>
-      <c r="R127" s="12" t="n"/>
+      <c r="P127" s="28" t="n"/>
+      <c r="Q127" s="12" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="12" t="inlineStr">
@@ -16911,16 +16415,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M128" s="12" t="inlineStr"/>
-      <c r="N128" s="27" t="inlineStr">
+      <c r="M128" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N128" s="12" t="n"/>
       <c r="O128" s="12" t="n"/>
-      <c r="P128" s="12" t="n"/>
-      <c r="Q128" s="28" t="n"/>
-      <c r="R128" s="12" t="n"/>
+      <c r="P128" s="28" t="n"/>
+      <c r="Q128" s="12" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="12" t="inlineStr">
@@ -16983,16 +16486,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M129" s="12" t="inlineStr"/>
-      <c r="N129" s="27" t="inlineStr">
+      <c r="M129" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N129" s="12" t="n"/>
       <c r="O129" s="12" t="n"/>
-      <c r="P129" s="12" t="n"/>
-      <c r="Q129" s="28" t="n"/>
-      <c r="R129" s="12" t="n"/>
+      <c r="P129" s="28" t="n"/>
+      <c r="Q129" s="12" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="12" t="inlineStr">
@@ -17056,16 +16558,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M130" s="12" t="inlineStr"/>
-      <c r="N130" s="27" t="inlineStr">
+      <c r="M130" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N130" s="12" t="n"/>
       <c r="O130" s="12" t="n"/>
-      <c r="P130" s="12" t="n"/>
-      <c r="Q130" s="28" t="n"/>
-      <c r="R130" s="12" t="n"/>
+      <c r="P130" s="28" t="n"/>
+      <c r="Q130" s="12" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="12" t="inlineStr">
@@ -17128,16 +16629,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M131" s="12" t="inlineStr"/>
-      <c r="N131" s="27" t="inlineStr">
+      <c r="M131" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N131" s="12" t="n"/>
       <c r="O131" s="12" t="n"/>
-      <c r="P131" s="12" t="n"/>
-      <c r="Q131" s="28" t="n"/>
-      <c r="R131" s="12" t="n"/>
+      <c r="P131" s="28" t="n"/>
+      <c r="Q131" s="12" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="12" t="inlineStr">
@@ -17200,16 +16700,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M132" s="12" t="inlineStr"/>
-      <c r="N132" s="27" t="inlineStr">
+      <c r="M132" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N132" s="12" t="n"/>
       <c r="O132" s="12" t="n"/>
-      <c r="P132" s="12" t="n"/>
-      <c r="Q132" s="28" t="n"/>
-      <c r="R132" s="12" t="n"/>
+      <c r="P132" s="28" t="n"/>
+      <c r="Q132" s="12" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="12" t="inlineStr">
@@ -17272,16 +16771,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M133" s="12" t="inlineStr"/>
-      <c r="N133" s="27" t="inlineStr">
+      <c r="M133" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N133" s="12" t="n"/>
       <c r="O133" s="12" t="n"/>
-      <c r="P133" s="12" t="n"/>
-      <c r="Q133" s="28" t="n"/>
-      <c r="R133" s="12" t="n"/>
+      <c r="P133" s="28" t="n"/>
+      <c r="Q133" s="12" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="12" t="inlineStr">
@@ -17345,16 +16843,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M134" s="12" t="inlineStr"/>
-      <c r="N134" s="27" t="inlineStr">
+      <c r="M134" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N134" s="12" t="n"/>
       <c r="O134" s="12" t="n"/>
-      <c r="P134" s="12" t="n"/>
-      <c r="Q134" s="28" t="n"/>
-      <c r="R134" s="12" t="n"/>
+      <c r="P134" s="28" t="n"/>
+      <c r="Q134" s="12" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="12" t="inlineStr">
@@ -17417,16 +16914,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M135" s="12" t="inlineStr"/>
-      <c r="N135" s="27" t="inlineStr">
+      <c r="M135" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N135" s="12" t="n"/>
       <c r="O135" s="12" t="n"/>
-      <c r="P135" s="12" t="n"/>
-      <c r="Q135" s="28" t="n"/>
-      <c r="R135" s="12" t="n"/>
+      <c r="P135" s="28" t="n"/>
+      <c r="Q135" s="12" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="12" t="inlineStr">
@@ -17489,16 +16985,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M136" s="12" t="inlineStr"/>
-      <c r="N136" s="27" t="inlineStr">
+      <c r="M136" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N136" s="12" t="n"/>
       <c r="O136" s="12" t="n"/>
-      <c r="P136" s="12" t="n"/>
-      <c r="Q136" s="28" t="n"/>
-      <c r="R136" s="12" t="n"/>
+      <c r="P136" s="28" t="n"/>
+      <c r="Q136" s="12" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="12" t="inlineStr">
@@ -17562,16 +17057,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M137" s="12" t="inlineStr"/>
-      <c r="N137" s="27" t="inlineStr">
+      <c r="M137" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N137" s="12" t="n"/>
       <c r="O137" s="12" t="n"/>
-      <c r="P137" s="12" t="n"/>
-      <c r="Q137" s="28" t="n"/>
-      <c r="R137" s="12" t="n"/>
+      <c r="P137" s="28" t="n"/>
+      <c r="Q137" s="12" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="12" t="inlineStr">
@@ -17634,16 +17128,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M138" s="12" t="inlineStr"/>
-      <c r="N138" s="27" t="inlineStr">
+      <c r="M138" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N138" s="12" t="n"/>
       <c r="O138" s="12" t="n"/>
-      <c r="P138" s="12" t="n"/>
-      <c r="Q138" s="28" t="n"/>
-      <c r="R138" s="12" t="n"/>
+      <c r="P138" s="28" t="n"/>
+      <c r="Q138" s="12" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="12" t="inlineStr">
@@ -17706,16 +17199,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M139" s="12" t="inlineStr"/>
-      <c r="N139" s="27" t="inlineStr">
+      <c r="M139" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N139" s="12" t="n"/>
       <c r="O139" s="12" t="n"/>
-      <c r="P139" s="12" t="n"/>
-      <c r="Q139" s="28" t="n"/>
-      <c r="R139" s="12" t="n"/>
+      <c r="P139" s="28" t="n"/>
+      <c r="Q139" s="12" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="12" t="inlineStr">
@@ -17778,16 +17270,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M140" s="12" t="inlineStr"/>
-      <c r="N140" s="27" t="inlineStr">
+      <c r="M140" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N140" s="12" t="n"/>
       <c r="O140" s="12" t="n"/>
-      <c r="P140" s="12" t="n"/>
-      <c r="Q140" s="28" t="n"/>
-      <c r="R140" s="12" t="n"/>
+      <c r="P140" s="28" t="n"/>
+      <c r="Q140" s="12" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="12" t="inlineStr">
@@ -17850,16 +17341,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M141" s="12" t="inlineStr"/>
-      <c r="N141" s="27" t="inlineStr">
+      <c r="M141" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N141" s="12" t="n"/>
       <c r="O141" s="12" t="n"/>
-      <c r="P141" s="12" t="n"/>
-      <c r="Q141" s="28" t="n"/>
-      <c r="R141" s="12" t="n"/>
+      <c r="P141" s="28" t="n"/>
+      <c r="Q141" s="12" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="12" t="inlineStr">
@@ -17923,16 +17413,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M142" s="12" t="inlineStr"/>
-      <c r="N142" s="27" t="inlineStr">
+      <c r="M142" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N142" s="12" t="n"/>
       <c r="O142" s="12" t="n"/>
-      <c r="P142" s="12" t="n"/>
-      <c r="Q142" s="28" t="n"/>
-      <c r="R142" s="12" t="n"/>
+      <c r="P142" s="28" t="n"/>
+      <c r="Q142" s="12" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="12" t="inlineStr">
@@ -17995,16 +17484,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M143" s="12" t="inlineStr"/>
-      <c r="N143" s="27" t="inlineStr">
+      <c r="M143" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N143" s="12" t="n"/>
       <c r="O143" s="12" t="n"/>
-      <c r="P143" s="12" t="n"/>
-      <c r="Q143" s="28" t="n"/>
-      <c r="R143" s="12" t="n"/>
+      <c r="P143" s="28" t="n"/>
+      <c r="Q143" s="12" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="12" t="inlineStr">
@@ -18067,16 +17555,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M144" s="12" t="inlineStr"/>
-      <c r="N144" s="27" t="inlineStr">
+      <c r="M144" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N144" s="12" t="n"/>
       <c r="O144" s="12" t="n"/>
-      <c r="P144" s="12" t="n"/>
-      <c r="Q144" s="28" t="n"/>
-      <c r="R144" s="12" t="n"/>
+      <c r="P144" s="28" t="n"/>
+      <c r="Q144" s="12" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="12" t="inlineStr">
@@ -18139,16 +17626,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M145" s="12" t="inlineStr"/>
-      <c r="N145" s="27" t="inlineStr">
+      <c r="M145" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N145" s="12" t="n"/>
       <c r="O145" s="12" t="n"/>
-      <c r="P145" s="12" t="n"/>
-      <c r="Q145" s="28" t="n"/>
-      <c r="R145" s="12" t="n"/>
+      <c r="P145" s="28" t="n"/>
+      <c r="Q145" s="12" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="12" t="inlineStr">
@@ -18211,16 +17697,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M146" s="12" t="inlineStr"/>
-      <c r="N146" s="27" t="inlineStr">
+      <c r="M146" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N146" s="12" t="n"/>
       <c r="O146" s="12" t="n"/>
-      <c r="P146" s="12" t="n"/>
-      <c r="Q146" s="28" t="n"/>
-      <c r="R146" s="12" t="n"/>
+      <c r="P146" s="28" t="n"/>
+      <c r="Q146" s="12" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="12" t="inlineStr">
@@ -18284,16 +17769,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M147" s="12" t="inlineStr"/>
-      <c r="N147" s="27" t="inlineStr">
+      <c r="M147" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N147" s="12" t="n"/>
       <c r="O147" s="12" t="n"/>
-      <c r="P147" s="12" t="n"/>
-      <c r="Q147" s="28" t="n"/>
-      <c r="R147" s="12" t="n"/>
+      <c r="P147" s="28" t="n"/>
+      <c r="Q147" s="12" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="12" t="inlineStr">
@@ -18357,16 +17841,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M148" s="12" t="inlineStr"/>
-      <c r="N148" s="27" t="inlineStr">
+      <c r="M148" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N148" s="12" t="n"/>
       <c r="O148" s="12" t="n"/>
-      <c r="P148" s="12" t="n"/>
-      <c r="Q148" s="28" t="n"/>
-      <c r="R148" s="12" t="n"/>
+      <c r="P148" s="28" t="n"/>
+      <c r="Q148" s="12" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="12" t="inlineStr">
@@ -18429,16 +17912,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M149" s="12" t="inlineStr"/>
-      <c r="N149" s="27" t="inlineStr">
+      <c r="M149" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N149" s="12" t="n"/>
       <c r="O149" s="12" t="n"/>
-      <c r="P149" s="12" t="n"/>
-      <c r="Q149" s="28" t="n"/>
-      <c r="R149" s="12" t="n"/>
+      <c r="P149" s="28" t="n"/>
+      <c r="Q149" s="12" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="12" t="inlineStr">
@@ -18501,16 +17983,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M150" s="12" t="inlineStr"/>
-      <c r="N150" s="27" t="inlineStr">
+      <c r="M150" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N150" s="12" t="n"/>
       <c r="O150" s="12" t="n"/>
-      <c r="P150" s="12" t="n"/>
-      <c r="Q150" s="28" t="n"/>
-      <c r="R150" s="12" t="n"/>
+      <c r="P150" s="28" t="n"/>
+      <c r="Q150" s="12" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="12" t="inlineStr">
@@ -18573,16 +18054,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M151" s="12" t="inlineStr"/>
-      <c r="N151" s="27" t="inlineStr">
+      <c r="M151" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N151" s="12" t="n"/>
       <c r="O151" s="12" t="n"/>
-      <c r="P151" s="12" t="n"/>
-      <c r="Q151" s="28" t="n"/>
-      <c r="R151" s="12" t="n"/>
+      <c r="P151" s="28" t="n"/>
+      <c r="Q151" s="12" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="12" t="inlineStr">
@@ -18645,16 +18125,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M152" s="12" t="inlineStr"/>
-      <c r="N152" s="27" t="inlineStr">
+      <c r="M152" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N152" s="12" t="n"/>
       <c r="O152" s="12" t="n"/>
-      <c r="P152" s="12" t="n"/>
-      <c r="Q152" s="28" t="n"/>
-      <c r="R152" s="12" t="n"/>
+      <c r="P152" s="28" t="n"/>
+      <c r="Q152" s="12" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="12" t="inlineStr">
@@ -18717,16 +18196,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M153" s="12" t="inlineStr"/>
-      <c r="N153" s="27" t="inlineStr">
+      <c r="M153" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N153" s="12" t="n"/>
       <c r="O153" s="12" t="n"/>
-      <c r="P153" s="12" t="n"/>
-      <c r="Q153" s="28" t="n"/>
-      <c r="R153" s="12" t="n"/>
+      <c r="P153" s="28" t="n"/>
+      <c r="Q153" s="12" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="12" t="inlineStr">
@@ -18789,16 +18267,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M154" s="12" t="inlineStr"/>
-      <c r="N154" s="27" t="inlineStr">
+      <c r="M154" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N154" s="12" t="n"/>
       <c r="O154" s="12" t="n"/>
-      <c r="P154" s="12" t="n"/>
-      <c r="Q154" s="28" t="n"/>
-      <c r="R154" s="12" t="n"/>
+      <c r="P154" s="28" t="n"/>
+      <c r="Q154" s="12" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="12" t="inlineStr">
@@ -18861,16 +18338,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M155" s="12" t="inlineStr"/>
-      <c r="N155" s="27" t="inlineStr">
+      <c r="M155" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N155" s="12" t="n"/>
       <c r="O155" s="12" t="n"/>
-      <c r="P155" s="12" t="n"/>
-      <c r="Q155" s="28" t="n"/>
-      <c r="R155" s="12" t="n"/>
+      <c r="P155" s="28" t="n"/>
+      <c r="Q155" s="12" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="12" t="inlineStr">
@@ -18933,16 +18409,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M156" s="12" t="inlineStr"/>
-      <c r="N156" s="27" t="inlineStr">
+      <c r="M156" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N156" s="12" t="n"/>
       <c r="O156" s="12" t="n"/>
-      <c r="P156" s="12" t="n"/>
-      <c r="Q156" s="28" t="n"/>
-      <c r="R156" s="12" t="n"/>
+      <c r="P156" s="28" t="n"/>
+      <c r="Q156" s="12" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="12" t="inlineStr">
@@ -19005,16 +18480,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M157" s="12" t="inlineStr"/>
-      <c r="N157" s="27" t="inlineStr">
+      <c r="M157" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N157" s="12" t="n"/>
       <c r="O157" s="12" t="n"/>
-      <c r="P157" s="12" t="n"/>
-      <c r="Q157" s="28" t="n"/>
-      <c r="R157" s="12" t="n"/>
+      <c r="P157" s="28" t="n"/>
+      <c r="Q157" s="12" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="12" t="inlineStr">
@@ -19077,16 +18551,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M158" s="12" t="inlineStr"/>
-      <c r="N158" s="27" t="inlineStr">
+      <c r="M158" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N158" s="12" t="n"/>
       <c r="O158" s="12" t="n"/>
-      <c r="P158" s="12" t="n"/>
-      <c r="Q158" s="28" t="n"/>
-      <c r="R158" s="12" t="n"/>
+      <c r="P158" s="28" t="n"/>
+      <c r="Q158" s="12" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="12" t="inlineStr">
@@ -19150,16 +18623,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M159" s="12" t="inlineStr"/>
-      <c r="N159" s="27" t="inlineStr">
+      <c r="M159" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N159" s="12" t="n"/>
       <c r="O159" s="12" t="n"/>
-      <c r="P159" s="12" t="n"/>
-      <c r="Q159" s="28" t="n"/>
-      <c r="R159" s="12" t="n"/>
+      <c r="P159" s="28" t="n"/>
+      <c r="Q159" s="12" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="12" t="inlineStr">
@@ -19222,16 +18694,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M160" s="12" t="inlineStr"/>
-      <c r="N160" s="27" t="inlineStr">
+      <c r="M160" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N160" s="12" t="n"/>
       <c r="O160" s="12" t="n"/>
-      <c r="P160" s="12" t="n"/>
-      <c r="Q160" s="28" t="n"/>
-      <c r="R160" s="12" t="n"/>
+      <c r="P160" s="28" t="n"/>
+      <c r="Q160" s="12" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="12" t="inlineStr">
@@ -19294,16 +18765,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M161" s="12" t="inlineStr"/>
-      <c r="N161" s="27" t="inlineStr">
+      <c r="M161" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N161" s="12" t="n"/>
       <c r="O161" s="12" t="n"/>
-      <c r="P161" s="12" t="n"/>
-      <c r="Q161" s="28" t="n"/>
-      <c r="R161" s="12" t="n"/>
+      <c r="P161" s="28" t="n"/>
+      <c r="Q161" s="12" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="12" t="inlineStr">
@@ -19366,16 +18836,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M162" s="12" t="inlineStr"/>
-      <c r="N162" s="27" t="inlineStr">
+      <c r="M162" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N162" s="12" t="n"/>
       <c r="O162" s="12" t="n"/>
-      <c r="P162" s="12" t="n"/>
-      <c r="Q162" s="28" t="n"/>
-      <c r="R162" s="12" t="n"/>
+      <c r="P162" s="28" t="n"/>
+      <c r="Q162" s="12" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="12" t="inlineStr">
@@ -19438,16 +18907,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M163" s="12" t="inlineStr"/>
-      <c r="N163" s="27" t="inlineStr">
+      <c r="M163" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N163" s="12" t="n"/>
       <c r="O163" s="12" t="n"/>
-      <c r="P163" s="12" t="n"/>
-      <c r="Q163" s="28" t="n"/>
-      <c r="R163" s="12" t="n"/>
+      <c r="P163" s="28" t="n"/>
+      <c r="Q163" s="12" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="12" t="inlineStr">
@@ -19511,16 +18979,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M164" s="12" t="inlineStr"/>
-      <c r="N164" s="27" t="inlineStr">
+      <c r="M164" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N164" s="12" t="n"/>
       <c r="O164" s="12" t="n"/>
-      <c r="P164" s="12" t="n"/>
-      <c r="Q164" s="28" t="n"/>
-      <c r="R164" s="12" t="n"/>
+      <c r="P164" s="28" t="n"/>
+      <c r="Q164" s="12" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="12" t="inlineStr">
@@ -19583,16 +19050,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M165" s="12" t="inlineStr"/>
-      <c r="N165" s="27" t="inlineStr">
+      <c r="M165" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N165" s="12" t="n"/>
       <c r="O165" s="12" t="n"/>
-      <c r="P165" s="12" t="n"/>
-      <c r="Q165" s="28" t="n"/>
-      <c r="R165" s="12" t="n"/>
+      <c r="P165" s="28" t="n"/>
+      <c r="Q165" s="12" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="12" t="inlineStr">
@@ -19655,16 +19121,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M166" s="12" t="inlineStr"/>
-      <c r="N166" s="27" t="inlineStr">
+      <c r="M166" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N166" s="12" t="n"/>
       <c r="O166" s="12" t="n"/>
-      <c r="P166" s="12" t="n"/>
-      <c r="Q166" s="28" t="n"/>
-      <c r="R166" s="12" t="n"/>
+      <c r="P166" s="28" t="n"/>
+      <c r="Q166" s="12" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="12" t="inlineStr">
@@ -19727,16 +19192,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M167" s="12" t="inlineStr"/>
-      <c r="N167" s="27" t="inlineStr">
+      <c r="M167" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N167" s="12" t="n"/>
       <c r="O167" s="12" t="n"/>
-      <c r="P167" s="12" t="n"/>
-      <c r="Q167" s="28" t="n"/>
-      <c r="R167" s="12" t="n"/>
+      <c r="P167" s="28" t="n"/>
+      <c r="Q167" s="12" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="12" t="inlineStr">
@@ -19799,16 +19263,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M168" s="12" t="inlineStr"/>
-      <c r="N168" s="27" t="inlineStr">
+      <c r="M168" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N168" s="12" t="n"/>
       <c r="O168" s="12" t="n"/>
-      <c r="P168" s="12" t="n"/>
-      <c r="Q168" s="28" t="n"/>
-      <c r="R168" s="12" t="n"/>
+      <c r="P168" s="28" t="n"/>
+      <c r="Q168" s="12" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="12" t="inlineStr">
@@ -19871,16 +19334,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M169" s="12" t="inlineStr"/>
-      <c r="N169" s="27" t="inlineStr">
+      <c r="M169" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N169" s="12" t="n"/>
       <c r="O169" s="12" t="n"/>
-      <c r="P169" s="12" t="n"/>
-      <c r="Q169" s="28" t="n"/>
-      <c r="R169" s="12" t="n"/>
+      <c r="P169" s="28" t="n"/>
+      <c r="Q169" s="12" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="12" t="inlineStr">
@@ -19943,16 +19405,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M170" s="12" t="inlineStr"/>
-      <c r="N170" s="27" t="inlineStr">
+      <c r="M170" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N170" s="12" t="n"/>
       <c r="O170" s="12" t="n"/>
-      <c r="P170" s="12" t="n"/>
-      <c r="Q170" s="28" t="n"/>
-      <c r="R170" s="12" t="n"/>
+      <c r="P170" s="28" t="n"/>
+      <c r="Q170" s="12" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="12" t="inlineStr">
@@ -20016,16 +19477,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M171" s="12" t="inlineStr"/>
-      <c r="N171" s="27" t="inlineStr">
+      <c r="M171" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N171" s="12" t="n"/>
       <c r="O171" s="12" t="n"/>
-      <c r="P171" s="12" t="n"/>
-      <c r="Q171" s="28" t="n"/>
-      <c r="R171" s="12" t="n"/>
+      <c r="P171" s="28" t="n"/>
+      <c r="Q171" s="12" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="12" t="inlineStr">
@@ -20088,16 +19548,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M172" s="12" t="inlineStr"/>
-      <c r="N172" s="27" t="inlineStr">
+      <c r="M172" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N172" s="12" t="n"/>
       <c r="O172" s="12" t="n"/>
-      <c r="P172" s="12" t="n"/>
-      <c r="Q172" s="28" t="n"/>
-      <c r="R172" s="12" t="n"/>
+      <c r="P172" s="28" t="n"/>
+      <c r="Q172" s="12" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="12" t="inlineStr">
@@ -20160,16 +19619,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M173" s="12" t="inlineStr"/>
-      <c r="N173" s="27" t="inlineStr">
+      <c r="M173" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N173" s="12" t="n"/>
       <c r="O173" s="12" t="n"/>
-      <c r="P173" s="12" t="n"/>
-      <c r="Q173" s="28" t="n"/>
-      <c r="R173" s="12" t="n"/>
+      <c r="P173" s="28" t="n"/>
+      <c r="Q173" s="12" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="12" t="inlineStr">
@@ -20232,16 +19690,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M174" s="12" t="inlineStr"/>
-      <c r="N174" s="27" t="inlineStr">
+      <c r="M174" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N174" s="12" t="n"/>
       <c r="O174" s="12" t="n"/>
-      <c r="P174" s="12" t="n"/>
-      <c r="Q174" s="28" t="n"/>
-      <c r="R174" s="12" t="n"/>
+      <c r="P174" s="28" t="n"/>
+      <c r="Q174" s="12" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="12" t="inlineStr">
@@ -20304,16 +19761,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M175" s="12" t="inlineStr"/>
-      <c r="N175" s="27" t="inlineStr">
+      <c r="M175" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N175" s="12" t="n"/>
       <c r="O175" s="12" t="n"/>
-      <c r="P175" s="12" t="n"/>
-      <c r="Q175" s="28" t="n"/>
-      <c r="R175" s="12" t="n"/>
+      <c r="P175" s="28" t="n"/>
+      <c r="Q175" s="12" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="12" t="inlineStr">
@@ -20377,16 +19833,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M176" s="12" t="inlineStr"/>
-      <c r="N176" s="27" t="inlineStr">
+      <c r="M176" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N176" s="12" t="n"/>
       <c r="O176" s="12" t="n"/>
-      <c r="P176" s="12" t="n"/>
-      <c r="Q176" s="28" t="n"/>
-      <c r="R176" s="12" t="n"/>
+      <c r="P176" s="28" t="n"/>
+      <c r="Q176" s="12" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="12" t="inlineStr">
@@ -20449,16 +19904,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M177" s="12" t="inlineStr"/>
-      <c r="N177" s="27" t="inlineStr">
+      <c r="M177" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N177" s="12" t="n"/>
       <c r="O177" s="12" t="n"/>
-      <c r="P177" s="12" t="n"/>
-      <c r="Q177" s="28" t="n"/>
-      <c r="R177" s="12" t="n"/>
+      <c r="P177" s="28" t="n"/>
+      <c r="Q177" s="12" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="12" t="inlineStr">
@@ -20521,16 +19975,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M178" s="12" t="inlineStr"/>
-      <c r="N178" s="27" t="inlineStr">
+      <c r="M178" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N178" s="12" t="n"/>
       <c r="O178" s="12" t="n"/>
-      <c r="P178" s="12" t="n"/>
-      <c r="Q178" s="28" t="n"/>
-      <c r="R178" s="12" t="n"/>
+      <c r="P178" s="28" t="n"/>
+      <c r="Q178" s="12" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="12" t="inlineStr">
@@ -20594,16 +20047,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M179" s="12" t="inlineStr"/>
-      <c r="N179" s="27" t="inlineStr">
+      <c r="M179" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N179" s="12" t="n"/>
       <c r="O179" s="12" t="n"/>
-      <c r="P179" s="12" t="n"/>
-      <c r="Q179" s="28" t="n"/>
-      <c r="R179" s="12" t="n"/>
+      <c r="P179" s="28" t="n"/>
+      <c r="Q179" s="12" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="12" t="inlineStr">
@@ -20666,16 +20118,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M180" s="12" t="inlineStr"/>
-      <c r="N180" s="27" t="inlineStr">
+      <c r="M180" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N180" s="12" t="n"/>
       <c r="O180" s="12" t="n"/>
-      <c r="P180" s="12" t="n"/>
-      <c r="Q180" s="28" t="n"/>
-      <c r="R180" s="12" t="n"/>
+      <c r="P180" s="28" t="n"/>
+      <c r="Q180" s="12" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="12" t="inlineStr">
@@ -20738,16 +20189,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M181" s="12" t="inlineStr"/>
-      <c r="N181" s="27" t="inlineStr">
+      <c r="M181" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N181" s="12" t="n"/>
       <c r="O181" s="12" t="n"/>
-      <c r="P181" s="12" t="n"/>
-      <c r="Q181" s="28" t="n"/>
-      <c r="R181" s="12" t="n"/>
+      <c r="P181" s="28" t="n"/>
+      <c r="Q181" s="12" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="12" t="inlineStr">
@@ -20797,12 +20247,12 @@
       </c>
       <c r="J182" s="12" t="inlineStr">
         <is>
-          <t>1. As cl.officer1 look for the extract; call the run endpoint.</t>
+          <t>1. As cl.officer1 look for the extract; send a direct run request.</t>
         </is>
       </c>
       <c r="K182" s="12" t="inlineStr">
         <is>
-          <t>The report is not listed; the call returns HTTP 403.
+          <t>The report is not listed; the request is refused.
 Message "You are not permitted to perform this action".</t>
         </is>
       </c>
@@ -20811,16 +20261,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M182" s="12" t="inlineStr"/>
-      <c r="N182" s="27" t="inlineStr">
+      <c r="M182" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N182" s="12" t="n"/>
       <c r="O182" s="12" t="n"/>
-      <c r="P182" s="12" t="n"/>
-      <c r="Q182" s="28" t="n"/>
-      <c r="R182" s="12" t="n"/>
+      <c r="P182" s="28" t="n"/>
+      <c r="Q182" s="12" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="12" t="inlineStr">
@@ -20883,16 +20332,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M183" s="12" t="inlineStr"/>
-      <c r="N183" s="27" t="inlineStr">
+      <c r="M183" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N183" s="12" t="n"/>
       <c r="O183" s="12" t="n"/>
-      <c r="P183" s="12" t="n"/>
-      <c r="Q183" s="28" t="n"/>
-      <c r="R183" s="12" t="n"/>
+      <c r="P183" s="28" t="n"/>
+      <c r="Q183" s="12" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="12" t="inlineStr">
@@ -20942,12 +20390,12 @@
       </c>
       <c r="J184" s="12" t="inlineStr">
         <is>
-          <t>1. Look for Export; call the export endpoint.</t>
+          <t>1. Look for Export; send a direct export request.</t>
         </is>
       </c>
       <c r="K184" s="12" t="inlineStr">
         <is>
-          <t>Export is not shown; the call is refused.
+          <t>Export is not shown; a direct request is refused.
 Message "You are not permitted to perform this action".</t>
         </is>
       </c>
@@ -20956,16 +20404,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M184" s="12" t="inlineStr"/>
-      <c r="N184" s="27" t="inlineStr">
+      <c r="M184" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N184" s="12" t="n"/>
       <c r="O184" s="12" t="n"/>
-      <c r="P184" s="12" t="n"/>
-      <c r="Q184" s="28" t="n"/>
-      <c r="R184" s="12" t="n"/>
+      <c r="P184" s="28" t="n"/>
+      <c r="Q184" s="12" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="12" t="inlineStr">
@@ -21028,16 +20475,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M185" s="12" t="inlineStr"/>
-      <c r="N185" s="27" t="inlineStr">
+      <c r="M185" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N185" s="12" t="n"/>
       <c r="O185" s="12" t="n"/>
-      <c r="P185" s="12" t="n"/>
-      <c r="Q185" s="28" t="n"/>
-      <c r="R185" s="12" t="n"/>
+      <c r="P185" s="28" t="n"/>
+      <c r="Q185" s="12" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="12" t="inlineStr">
@@ -21077,7 +20523,7 @@
       </c>
       <c r="H186" s="12" t="inlineStr">
         <is>
-          <t>API call with the user's token (tester tool, for example Postman)</t>
+          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I186" s="12" t="inlineStr">
@@ -21087,12 +20533,12 @@
       </c>
       <c r="J186" s="12" t="inlineStr">
         <is>
-          <t>1. Type the address of a claim record; call GET on the claim.</t>
+          <t>1. Type the address of a claim record; send a direct request to open the claim.</t>
         </is>
       </c>
       <c r="K186" s="12" t="inlineStr">
         <is>
-          <t>The no-access page is shown; the call returns HTTP 403.</t>
+          <t>The no-access page is shown; the request is refused.</t>
         </is>
       </c>
       <c r="L186" s="12" t="inlineStr">
@@ -21100,16 +20546,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M186" s="12" t="inlineStr"/>
-      <c r="N186" s="27" t="inlineStr">
+      <c r="M186" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N186" s="12" t="n"/>
       <c r="O186" s="12" t="n"/>
-      <c r="P186" s="12" t="n"/>
-      <c r="Q186" s="28" t="n"/>
-      <c r="R186" s="12" t="n"/>
+      <c r="P186" s="28" t="n"/>
+      <c r="Q186" s="12" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="12" t="inlineStr">
@@ -21172,16 +20617,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M187" s="12" t="inlineStr"/>
-      <c r="N187" s="27" t="inlineStr">
+      <c r="M187" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N187" s="12" t="n"/>
       <c r="O187" s="12" t="n"/>
-      <c r="P187" s="12" t="n"/>
-      <c r="Q187" s="28" t="n"/>
-      <c r="R187" s="12" t="n"/>
+      <c r="P187" s="28" t="n"/>
+      <c r="Q187" s="12" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="12" t="inlineStr">
@@ -21244,16 +20688,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M188" s="12" t="inlineStr"/>
-      <c r="N188" s="27" t="inlineStr">
+      <c r="M188" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N188" s="12" t="n"/>
       <c r="O188" s="12" t="n"/>
-      <c r="P188" s="12" t="n"/>
-      <c r="Q188" s="28" t="n"/>
-      <c r="R188" s="12" t="n"/>
+      <c r="P188" s="28" t="n"/>
+      <c r="Q188" s="12" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="12" t="inlineStr">
@@ -21317,23 +20760,22 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M189" s="12" t="inlineStr"/>
-      <c r="N189" s="27" t="inlineStr">
+      <c r="M189" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N189" s="12" t="n"/>
       <c r="O189" s="12" t="n"/>
-      <c r="P189" s="12" t="n"/>
-      <c r="Q189" s="28" t="n"/>
-      <c r="R189" s="12" t="n"/>
+      <c r="P189" s="28" t="n"/>
+      <c r="Q189" s="12" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:R189"/>
+  <autoFilter ref="A4:Q189"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:R2"/>
+    <mergeCell ref="A2:Q2"/>
   </mergeCells>
-  <conditionalFormatting sqref="N5:N689">
+  <conditionalFormatting sqref="M5:M689">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="1" stopIfTrue="1">
       <formula>"Pass"</formula>
     </cfRule>
@@ -21347,19 +20789,19 @@
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:R689">
+  <conditionalFormatting sqref="A5:Q689">
     <cfRule type="expression" priority="5" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation sqref="F5:F689" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Type" error="Choose a value from the list (Type)." type="list">
-      <formula1>'_lists'!$B$1:$B$7</formula1>
+      <formula1>'_lists'!$B$1:$B$9</formula1>
     </dataValidation>
     <dataValidation sqref="L5:L689" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Priority" error="Choose a value from the list (Priority)." type="list">
       <formula1>'_lists'!$C$1:$C$3</formula1>
     </dataValidation>
-    <dataValidation sqref="N5:N689" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
+    <dataValidation sqref="M5:M689" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
       <formula1>'_lists'!$D$1:$D$5</formula1>
     </dataValidation>
   </dataValidations>
@@ -21383,7 +20825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J95"/>
+  <dimension ref="A1:I95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -21395,7 +20837,6 @@
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -21422,7 +20863,6 @@
       <c r="G3" s="25" t="n"/>
       <c r="H3" s="25" t="n"/>
       <c r="I3" s="25" t="n"/>
-      <c r="J3" s="25" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
@@ -21467,11 +20907,6 @@
       </c>
       <c r="I4" s="26" t="inlineStr">
         <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="J4" s="26" t="inlineStr">
-        <is>
           <t>Coverage</t>
         </is>
       </c>
@@ -21509,10 +20944,7 @@
       <c r="H5" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I5" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="27" t="inlineStr">
+      <c r="I5" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -21551,10 +20983,7 @@
       <c r="H6" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="27" t="inlineStr">
+      <c r="I6" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -21593,10 +21022,7 @@
       <c r="H7" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="27" t="inlineStr">
+      <c r="I7" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -21635,10 +21061,7 @@
       <c r="H8" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I8" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="27" t="inlineStr">
+      <c r="I8" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -21677,10 +21100,7 @@
       <c r="H9" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="27" t="inlineStr">
+      <c r="I9" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -21719,10 +21139,7 @@
       <c r="H10" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I10" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="27" t="inlineStr">
+      <c r="I10" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -21761,10 +21178,7 @@
       <c r="H11" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="27" t="inlineStr">
+      <c r="I11" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -21803,10 +21217,7 @@
       <c r="H12" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="27" t="inlineStr">
+      <c r="I12" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -21845,10 +21256,7 @@
       <c r="H13" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="27" t="inlineStr">
+      <c r="I13" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -21887,10 +21295,7 @@
       <c r="H14" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I14" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="27" t="inlineStr">
+      <c r="I14" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -21929,10 +21334,7 @@
       <c r="H15" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="27" t="inlineStr">
+      <c r="I15" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -21971,10 +21373,7 @@
       <c r="H16" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="27" t="inlineStr">
+      <c r="I16" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22013,10 +21412,7 @@
       <c r="H17" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="27" t="inlineStr">
+      <c r="I17" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22055,10 +21451,7 @@
       <c r="H18" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="27" t="inlineStr">
+      <c r="I18" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22097,10 +21490,7 @@
       <c r="H19" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="27" t="inlineStr">
+      <c r="I19" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22139,10 +21529,7 @@
       <c r="H20" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="27" t="inlineStr">
+      <c r="I20" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22181,10 +21568,7 @@
       <c r="H21" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="27" t="inlineStr">
+      <c r="I21" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22223,10 +21607,7 @@
       <c r="H22" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="27" t="inlineStr">
+      <c r="I22" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22265,10 +21646,7 @@
       <c r="H23" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="27" t="inlineStr">
+      <c r="I23" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22307,10 +21685,7 @@
       <c r="H24" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="27" t="inlineStr">
+      <c r="I24" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22349,10 +21724,7 @@
       <c r="H25" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="27" t="inlineStr">
+      <c r="I25" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22391,10 +21763,7 @@
       <c r="H26" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I26" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="27" t="inlineStr">
+      <c r="I26" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22433,10 +21802,7 @@
       <c r="H27" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I27" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="27" t="inlineStr">
+      <c r="I27" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22475,10 +21841,7 @@
       <c r="H28" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I28" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="27" t="inlineStr">
+      <c r="I28" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22517,10 +21880,7 @@
       <c r="H29" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="27" t="inlineStr">
+      <c r="I29" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22559,10 +21919,7 @@
       <c r="H30" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="27" t="inlineStr">
+      <c r="I30" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22601,10 +21958,7 @@
       <c r="H31" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="27" t="inlineStr">
+      <c r="I31" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22643,10 +21997,7 @@
       <c r="H32" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="27" t="inlineStr">
+      <c r="I32" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22685,10 +22036,7 @@
       <c r="H33" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="27" t="inlineStr">
+      <c r="I33" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22727,10 +22075,7 @@
       <c r="H34" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="27" t="inlineStr">
+      <c r="I34" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22769,10 +22114,7 @@
       <c r="H35" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="27" t="inlineStr">
+      <c r="I35" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22811,10 +22153,7 @@
       <c r="H36" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I36" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="27" t="inlineStr">
+      <c r="I36" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22853,10 +22192,7 @@
       <c r="H37" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I37" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="27" t="inlineStr">
+      <c r="I37" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22895,10 +22231,7 @@
       <c r="H38" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I38" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="27" t="inlineStr">
+      <c r="I38" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22937,10 +22270,7 @@
       <c r="H39" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I39" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="27" t="inlineStr">
+      <c r="I39" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22979,10 +22309,7 @@
       <c r="H40" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="27" t="inlineStr">
+      <c r="I40" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23021,10 +22348,7 @@
       <c r="H41" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I41" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="27" t="inlineStr">
+      <c r="I41" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23063,10 +22387,7 @@
       <c r="H42" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I42" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="27" t="inlineStr">
+      <c r="I42" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23105,10 +22426,7 @@
       <c r="H43" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I43" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="27" t="inlineStr">
+      <c r="I43" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23143,10 +22461,7 @@
       <c r="H44" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I44" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="27" t="inlineStr">
+      <c r="I44" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23181,10 +22496,7 @@
       <c r="H45" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I45" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="27" t="inlineStr">
+      <c r="I45" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23219,10 +22531,7 @@
       <c r="H46" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="I46" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="27" t="inlineStr">
+      <c r="I46" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23257,10 +22566,7 @@
       <c r="H47" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I47" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="27" t="inlineStr">
+      <c r="I47" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23295,10 +22601,7 @@
       <c r="H48" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I48" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="27" t="inlineStr">
+      <c r="I48" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23333,10 +22636,7 @@
       <c r="H49" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="27" t="inlineStr">
+      <c r="I49" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23371,10 +22671,7 @@
       <c r="H50" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I50" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="27" t="inlineStr">
+      <c r="I50" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23409,10 +22706,7 @@
       <c r="H51" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I51" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="27" t="inlineStr">
+      <c r="I51" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23447,10 +22741,7 @@
       <c r="H52" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I52" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="27" t="inlineStr">
+      <c r="I52" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23485,10 +22776,7 @@
       <c r="H53" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I53" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" s="27" t="inlineStr">
+      <c r="I53" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23523,10 +22811,7 @@
       <c r="H54" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I54" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="27" t="inlineStr">
+      <c r="I54" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23561,10 +22846,7 @@
       <c r="H55" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="27" t="inlineStr">
+      <c r="I55" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23599,10 +22881,7 @@
       <c r="H56" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I56" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="27" t="inlineStr">
+      <c r="I56" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23637,10 +22916,7 @@
       <c r="H57" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="27" t="inlineStr">
+      <c r="I57" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23675,10 +22951,7 @@
       <c r="H58" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I58" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="27" t="inlineStr">
+      <c r="I58" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23713,10 +22986,7 @@
       <c r="H59" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="27" t="inlineStr">
+      <c r="I59" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23751,10 +23021,7 @@
       <c r="H60" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I60" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="27" t="inlineStr">
+      <c r="I60" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23789,10 +23056,7 @@
       <c r="H61" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" s="27" t="inlineStr">
+      <c r="I61" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23827,10 +23091,7 @@
       <c r="H62" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I62" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="27" t="inlineStr">
+      <c r="I62" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23865,10 +23126,7 @@
       <c r="H63" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I63" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="27" t="inlineStr">
+      <c r="I63" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23903,10 +23161,7 @@
       <c r="H64" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I64" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="27" t="inlineStr">
+      <c r="I64" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23941,10 +23196,7 @@
       <c r="H65" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I65" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="27" t="inlineStr">
+      <c r="I65" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23979,10 +23231,7 @@
       <c r="H66" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I66" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" s="27" t="inlineStr">
+      <c r="I66" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24017,10 +23266,7 @@
       <c r="H67" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I67" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="27" t="inlineStr">
+      <c r="I67" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24055,10 +23301,7 @@
       <c r="H68" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I68" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="27" t="inlineStr">
+      <c r="I68" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24093,10 +23336,7 @@
       <c r="H69" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I69" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" s="27" t="inlineStr">
+      <c r="I69" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24131,10 +23371,7 @@
       <c r="H70" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I70" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" s="27" t="inlineStr">
+      <c r="I70" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24169,10 +23406,7 @@
       <c r="H71" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I71" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="27" t="inlineStr">
+      <c r="I71" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24207,10 +23441,7 @@
       <c r="H72" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I72" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" s="27" t="inlineStr">
+      <c r="I72" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24245,10 +23476,7 @@
       <c r="H73" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I73" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="27" t="inlineStr">
+      <c r="I73" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24283,10 +23511,7 @@
       <c r="H74" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I74" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" s="27" t="inlineStr">
+      <c r="I74" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24321,10 +23546,7 @@
       <c r="H75" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I75" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" s="27" t="inlineStr">
+      <c r="I75" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24359,10 +23581,7 @@
       <c r="H76" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I76" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="27" t="inlineStr">
+      <c r="I76" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24397,10 +23616,7 @@
       <c r="H77" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I77" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="27" t="inlineStr">
+      <c r="I77" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24435,10 +23651,7 @@
       <c r="H78" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I78" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="27" t="inlineStr">
+      <c r="I78" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24473,10 +23686,7 @@
       <c r="H79" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I79" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="27" t="inlineStr">
+      <c r="I79" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24511,10 +23721,7 @@
       <c r="H80" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I80" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" s="27" t="inlineStr">
+      <c r="I80" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24549,10 +23756,7 @@
       <c r="H81" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I81" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" s="27" t="inlineStr">
+      <c r="I81" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24587,10 +23791,7 @@
       <c r="H82" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I82" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" s="27" t="inlineStr">
+      <c r="I82" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24625,10 +23826,7 @@
       <c r="H83" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" s="27" t="inlineStr">
+      <c r="I83" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24663,10 +23861,7 @@
       <c r="H84" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I84" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" s="27" t="inlineStr">
+      <c r="I84" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24701,10 +23896,7 @@
       <c r="H85" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I85" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" s="27" t="inlineStr">
+      <c r="I85" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24739,10 +23931,7 @@
       <c r="H86" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I86" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="27" t="inlineStr">
+      <c r="I86" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24777,10 +23966,7 @@
       <c r="H87" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I87" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" s="27" t="inlineStr">
+      <c r="I87" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24815,10 +24001,7 @@
       <c r="H88" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I88" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" s="27" t="inlineStr">
+      <c r="I88" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24853,10 +24036,7 @@
       <c r="H89" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I89" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" s="27" t="inlineStr">
+      <c r="I89" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24891,10 +24071,7 @@
       <c r="H90" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I90" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" s="27" t="inlineStr">
+      <c r="I90" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24929,10 +24106,7 @@
       <c r="H91" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I91" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J91" s="27" t="inlineStr">
+      <c r="I91" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24967,10 +24141,7 @@
       <c r="H92" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I92" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J92" s="27" t="inlineStr">
+      <c r="I92" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -25005,10 +24176,7 @@
       <c r="H93" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I93" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J93" s="27" t="inlineStr">
+      <c r="I93" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -25043,10 +24211,7 @@
       <c r="H94" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I94" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J94" s="27" t="inlineStr">
+      <c r="I94" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -25081,32 +24246,29 @@
       <c r="H95" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I95" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J95" s="27" t="inlineStr">
+      <c r="I95" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J95"/>
+  <autoFilter ref="A4:I95"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="J5:J595">
+  <conditionalFormatting sqref="I5:I595">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="2" stopIfTrue="1">
       <formula>"GAP"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:J595">
+  <conditionalFormatting sqref="A5:I595">
     <cfRule type="expression" priority="2" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="J5:J595" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Coverage" error="Choose a value from the list (Coverage)." type="list">
+    <dataValidation sqref="I5:I595" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Coverage" error="Choose a value from the list (Coverage)." type="list">
       <formula1>'_lists'!$E$1:$E$2</formula1>
     </dataValidation>
   </dataValidations>
@@ -25331,7 +24493,7 @@
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Delivered list values of FRS section 9.2; register keyed in by cl.uh1</t>
+          <t>Seed data (list values of FRS section 9.2); register keyed in by cl.uh1</t>
         </is>
       </c>
       <c r="E10" s="12" t="n">
@@ -25443,7 +24605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M89"/>
+  <dimension ref="A1:L89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -25453,12 +24615,11 @@
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -25488,7 +24649,6 @@
       <c r="J3" s="25" t="n"/>
       <c r="K3" s="25" t="n"/>
       <c r="L3" s="25" t="n"/>
-      <c r="M3" s="25" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
@@ -25528,32 +24688,27 @@
       </c>
       <c r="H4" s="26" t="inlineStr">
         <is>
-          <t>Automation reference</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="I4" s="26" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Actual result</t>
         </is>
       </c>
       <c r="J4" s="26" t="inlineStr">
         <is>
-          <t>Actual result</t>
+          <t>Tester</t>
         </is>
       </c>
       <c r="K4" s="26" t="inlineStr">
         <is>
-          <t>Tester</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="L4" s="26" t="inlineStr">
         <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="M4" s="26" t="inlineStr">
-        <is>
-          <t>Defect ID</t>
+          <t>Issue ID</t>
         </is>
       </c>
     </row>
@@ -25593,16 +24748,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H5" s="12" t="inlineStr"/>
-      <c r="I5" s="27" t="inlineStr">
+      <c r="H5" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I5" s="12" t="n"/>
       <c r="J5" s="12" t="n"/>
-      <c r="K5" s="12" t="n"/>
-      <c r="L5" s="28" t="n"/>
-      <c r="M5" s="12" t="n"/>
+      <c r="K5" s="28" t="n"/>
+      <c r="L5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
@@ -25640,16 +24794,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H6" s="12" t="inlineStr"/>
-      <c r="I6" s="27" t="inlineStr">
+      <c r="H6" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I6" s="12" t="n"/>
       <c r="J6" s="12" t="n"/>
-      <c r="K6" s="12" t="n"/>
-      <c r="L6" s="28" t="n"/>
-      <c r="M6" s="12" t="n"/>
+      <c r="K6" s="28" t="n"/>
+      <c r="L6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
@@ -25687,16 +24840,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H7" s="12" t="inlineStr"/>
-      <c r="I7" s="27" t="inlineStr">
+      <c r="H7" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I7" s="12" t="n"/>
       <c r="J7" s="12" t="n"/>
-      <c r="K7" s="12" t="n"/>
-      <c r="L7" s="28" t="n"/>
-      <c r="M7" s="12" t="n"/>
+      <c r="K7" s="28" t="n"/>
+      <c r="L7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
@@ -25734,16 +24886,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H8" s="12" t="inlineStr"/>
-      <c r="I8" s="27" t="inlineStr">
+      <c r="H8" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I8" s="12" t="n"/>
       <c r="J8" s="12" t="n"/>
-      <c r="K8" s="12" t="n"/>
-      <c r="L8" s="28" t="n"/>
-      <c r="M8" s="12" t="n"/>
+      <c r="K8" s="28" t="n"/>
+      <c r="L8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
@@ -25781,16 +24932,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H9" s="12" t="inlineStr"/>
-      <c r="I9" s="27" t="inlineStr">
+      <c r="H9" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I9" s="12" t="n"/>
       <c r="J9" s="12" t="n"/>
-      <c r="K9" s="12" t="n"/>
-      <c r="L9" s="28" t="n"/>
-      <c r="M9" s="12" t="n"/>
+      <c r="K9" s="28" t="n"/>
+      <c r="L9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
@@ -25828,16 +24978,15 @@
           <t>Cover Lookup is not in the menu; the address shows the no-access page.</t>
         </is>
       </c>
-      <c r="H10" s="12" t="inlineStr"/>
-      <c r="I10" s="27" t="inlineStr">
+      <c r="H10" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I10" s="12" t="n"/>
       <c r="J10" s="12" t="n"/>
-      <c r="K10" s="12" t="n"/>
-      <c r="L10" s="28" t="n"/>
-      <c r="M10" s="12" t="n"/>
+      <c r="K10" s="28" t="n"/>
+      <c r="L10" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
@@ -25875,16 +25024,15 @@
           <t>Cover Lookup is not in the menu; the address shows the no-access page.</t>
         </is>
       </c>
-      <c r="H11" s="12" t="inlineStr"/>
-      <c r="I11" s="27" t="inlineStr">
+      <c r="H11" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I11" s="12" t="n"/>
       <c r="J11" s="12" t="n"/>
-      <c r="K11" s="12" t="n"/>
-      <c r="L11" s="28" t="n"/>
-      <c r="M11" s="12" t="n"/>
+      <c r="K11" s="28" t="n"/>
+      <c r="L11" s="12" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
@@ -25922,16 +25070,15 @@
           <t>Cover Lookup is not in the menu; the address shows the no-access page.</t>
         </is>
       </c>
-      <c r="H12" s="12" t="inlineStr"/>
-      <c r="I12" s="27" t="inlineStr">
+      <c r="H12" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I12" s="12" t="n"/>
       <c r="J12" s="12" t="n"/>
-      <c r="K12" s="12" t="n"/>
-      <c r="L12" s="28" t="n"/>
-      <c r="M12" s="12" t="n"/>
+      <c r="K12" s="28" t="n"/>
+      <c r="L12" s="12" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
@@ -25969,16 +25116,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H13" s="12" t="inlineStr"/>
-      <c r="I13" s="27" t="inlineStr">
+      <c r="H13" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I13" s="12" t="n"/>
       <c r="J13" s="12" t="n"/>
-      <c r="K13" s="12" t="n"/>
-      <c r="L13" s="28" t="n"/>
-      <c r="M13" s="12" t="n"/>
+      <c r="K13" s="28" t="n"/>
+      <c r="L13" s="12" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
@@ -26016,16 +25162,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H14" s="12" t="inlineStr"/>
-      <c r="I14" s="27" t="inlineStr">
+      <c r="H14" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I14" s="12" t="n"/>
       <c r="J14" s="12" t="n"/>
-      <c r="K14" s="12" t="n"/>
-      <c r="L14" s="28" t="n"/>
-      <c r="M14" s="12" t="n"/>
+      <c r="K14" s="28" t="n"/>
+      <c r="L14" s="12" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
@@ -26063,16 +25208,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H15" s="12" t="inlineStr"/>
-      <c r="I15" s="27" t="inlineStr">
+      <c r="H15" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I15" s="12" t="n"/>
       <c r="J15" s="12" t="n"/>
-      <c r="K15" s="12" t="n"/>
-      <c r="L15" s="28" t="n"/>
-      <c r="M15" s="12" t="n"/>
+      <c r="K15" s="28" t="n"/>
+      <c r="L15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
@@ -26107,19 +25251,18 @@
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
-          <t>Record Claim is not in the menu; the create call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H16" s="12" t="inlineStr"/>
-      <c r="I16" s="27" t="inlineStr">
+          <t>Record Claim is not in the menu; a direct create request is refused.</t>
+        </is>
+      </c>
+      <c r="H16" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I16" s="12" t="n"/>
       <c r="J16" s="12" t="n"/>
-      <c r="K16" s="12" t="n"/>
-      <c r="L16" s="28" t="n"/>
-      <c r="M16" s="12" t="n"/>
+      <c r="K16" s="28" t="n"/>
+      <c r="L16" s="12" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
@@ -26154,19 +25297,18 @@
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>Record Claim is not in the menu; the create call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H17" s="12" t="inlineStr"/>
-      <c r="I17" s="27" t="inlineStr">
+          <t>Record Claim is not in the menu; a direct create request is refused.</t>
+        </is>
+      </c>
+      <c r="H17" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I17" s="12" t="n"/>
       <c r="J17" s="12" t="n"/>
-      <c r="K17" s="12" t="n"/>
-      <c r="L17" s="28" t="n"/>
-      <c r="M17" s="12" t="n"/>
+      <c r="K17" s="28" t="n"/>
+      <c r="L17" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
@@ -26201,19 +25343,18 @@
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>Record Claim is not in the menu; the create call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H18" s="12" t="inlineStr"/>
-      <c r="I18" s="27" t="inlineStr">
+          <t>Record Claim is not in the menu; a direct create request is refused.</t>
+        </is>
+      </c>
+      <c r="H18" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I18" s="12" t="n"/>
       <c r="J18" s="12" t="n"/>
-      <c r="K18" s="12" t="n"/>
-      <c r="L18" s="28" t="n"/>
-      <c r="M18" s="12" t="n"/>
+      <c r="K18" s="28" t="n"/>
+      <c r="L18" s="12" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
@@ -26251,16 +25392,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H19" s="12" t="inlineStr"/>
-      <c r="I19" s="27" t="inlineStr">
+      <c r="H19" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I19" s="12" t="n"/>
       <c r="J19" s="12" t="n"/>
-      <c r="K19" s="12" t="n"/>
-      <c r="L19" s="28" t="n"/>
-      <c r="M19" s="12" t="n"/>
+      <c r="K19" s="28" t="n"/>
+      <c r="L19" s="12" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
@@ -26298,16 +25438,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H20" s="12" t="inlineStr"/>
-      <c r="I20" s="27" t="inlineStr">
+      <c r="H20" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I20" s="12" t="n"/>
       <c r="J20" s="12" t="n"/>
-      <c r="K20" s="12" t="n"/>
-      <c r="L20" s="28" t="n"/>
-      <c r="M20" s="12" t="n"/>
+      <c r="K20" s="28" t="n"/>
+      <c r="L20" s="12" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
@@ -26345,16 +25484,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H21" s="12" t="inlineStr"/>
-      <c r="I21" s="27" t="inlineStr">
+      <c r="H21" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I21" s="12" t="n"/>
       <c r="J21" s="12" t="n"/>
-      <c r="K21" s="12" t="n"/>
-      <c r="L21" s="28" t="n"/>
-      <c r="M21" s="12" t="n"/>
+      <c r="K21" s="28" t="n"/>
+      <c r="L21" s="12" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
@@ -26392,16 +25530,15 @@
           <t>Generate Authorization Code is not shown.</t>
         </is>
       </c>
-      <c r="H22" s="12" t="inlineStr"/>
-      <c r="I22" s="27" t="inlineStr">
+      <c r="H22" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I22" s="12" t="n"/>
       <c r="J22" s="12" t="n"/>
-      <c r="K22" s="12" t="n"/>
-      <c r="L22" s="28" t="n"/>
-      <c r="M22" s="12" t="n"/>
+      <c r="K22" s="28" t="n"/>
+      <c r="L22" s="12" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
@@ -26439,16 +25576,15 @@
           <t>Generate Authorization Code is not shown.</t>
         </is>
       </c>
-      <c r="H23" s="12" t="inlineStr"/>
-      <c r="I23" s="27" t="inlineStr">
+      <c r="H23" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I23" s="12" t="n"/>
       <c r="J23" s="12" t="n"/>
-      <c r="K23" s="12" t="n"/>
-      <c r="L23" s="28" t="n"/>
-      <c r="M23" s="12" t="n"/>
+      <c r="K23" s="28" t="n"/>
+      <c r="L23" s="12" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
@@ -26486,16 +25622,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H24" s="12" t="inlineStr"/>
-      <c r="I24" s="27" t="inlineStr">
+      <c r="H24" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I24" s="12" t="n"/>
       <c r="J24" s="12" t="n"/>
-      <c r="K24" s="12" t="n"/>
-      <c r="L24" s="28" t="n"/>
-      <c r="M24" s="12" t="n"/>
+      <c r="K24" s="28" t="n"/>
+      <c r="L24" s="12" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
@@ -26533,16 +25668,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H25" s="12" t="inlineStr"/>
-      <c r="I25" s="27" t="inlineStr">
+      <c r="H25" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I25" s="12" t="n"/>
       <c r="J25" s="12" t="n"/>
-      <c r="K25" s="12" t="n"/>
-      <c r="L25" s="28" t="n"/>
-      <c r="M25" s="12" t="n"/>
+      <c r="K25" s="28" t="n"/>
+      <c r="L25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
@@ -26580,16 +25714,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H26" s="12" t="inlineStr"/>
-      <c r="I26" s="27" t="inlineStr">
+      <c r="H26" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I26" s="12" t="n"/>
       <c r="J26" s="12" t="n"/>
-      <c r="K26" s="12" t="n"/>
-      <c r="L26" s="28" t="n"/>
-      <c r="M26" s="12" t="n"/>
+      <c r="K26" s="28" t="n"/>
+      <c r="L26" s="12" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
@@ -26627,16 +25760,15 @@
           <t>Change Status is not shown.</t>
         </is>
       </c>
-      <c r="H27" s="12" t="inlineStr"/>
-      <c r="I27" s="27" t="inlineStr">
+      <c r="H27" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I27" s="12" t="n"/>
       <c r="J27" s="12" t="n"/>
-      <c r="K27" s="12" t="n"/>
-      <c r="L27" s="28" t="n"/>
-      <c r="M27" s="12" t="n"/>
+      <c r="K27" s="28" t="n"/>
+      <c r="L27" s="12" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
@@ -26674,16 +25806,15 @@
           <t>Change Status is not shown.</t>
         </is>
       </c>
-      <c r="H28" s="12" t="inlineStr"/>
-      <c r="I28" s="27" t="inlineStr">
+      <c r="H28" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I28" s="12" t="n"/>
       <c r="J28" s="12" t="n"/>
-      <c r="K28" s="12" t="n"/>
-      <c r="L28" s="28" t="n"/>
-      <c r="M28" s="12" t="n"/>
+      <c r="K28" s="28" t="n"/>
+      <c r="L28" s="12" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
@@ -26721,16 +25852,15 @@
           <t>Change Status is not shown.</t>
         </is>
       </c>
-      <c r="H29" s="12" t="inlineStr"/>
-      <c r="I29" s="27" t="inlineStr">
+      <c r="H29" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I29" s="12" t="n"/>
       <c r="J29" s="12" t="n"/>
-      <c r="K29" s="12" t="n"/>
-      <c r="L29" s="28" t="n"/>
-      <c r="M29" s="12" t="n"/>
+      <c r="K29" s="28" t="n"/>
+      <c r="L29" s="12" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
@@ -26768,16 +25898,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H30" s="12" t="inlineStr"/>
-      <c r="I30" s="27" t="inlineStr">
+      <c r="H30" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I30" s="12" t="n"/>
       <c r="J30" s="12" t="n"/>
-      <c r="K30" s="12" t="n"/>
-      <c r="L30" s="28" t="n"/>
-      <c r="M30" s="12" t="n"/>
+      <c r="K30" s="28" t="n"/>
+      <c r="L30" s="12" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
@@ -26815,16 +25944,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H31" s="12" t="inlineStr"/>
-      <c r="I31" s="27" t="inlineStr">
+      <c r="H31" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I31" s="12" t="n"/>
       <c r="J31" s="12" t="n"/>
-      <c r="K31" s="12" t="n"/>
-      <c r="L31" s="28" t="n"/>
-      <c r="M31" s="12" t="n"/>
+      <c r="K31" s="28" t="n"/>
+      <c r="L31" s="12" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
@@ -26862,16 +25990,15 @@
           <t>Closing settlement types are refused with "You are not permitted to perform this action".</t>
         </is>
       </c>
-      <c r="H32" s="12" t="inlineStr"/>
-      <c r="I32" s="27" t="inlineStr">
+      <c r="H32" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I32" s="12" t="n"/>
       <c r="J32" s="12" t="n"/>
-      <c r="K32" s="12" t="n"/>
-      <c r="L32" s="28" t="n"/>
-      <c r="M32" s="12" t="n"/>
+      <c r="K32" s="28" t="n"/>
+      <c r="L32" s="12" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
@@ -26909,16 +26036,15 @@
           <t>Closing settlement types are refused with "You are not permitted to perform this action".</t>
         </is>
       </c>
-      <c r="H33" s="12" t="inlineStr"/>
-      <c r="I33" s="27" t="inlineStr">
+      <c r="H33" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I33" s="12" t="n"/>
       <c r="J33" s="12" t="n"/>
-      <c r="K33" s="12" t="n"/>
-      <c r="L33" s="28" t="n"/>
-      <c r="M33" s="12" t="n"/>
+      <c r="K33" s="28" t="n"/>
+      <c r="L33" s="12" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
@@ -26956,16 +26082,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H34" s="12" t="inlineStr"/>
-      <c r="I34" s="27" t="inlineStr">
+      <c r="H34" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I34" s="12" t="n"/>
       <c r="J34" s="12" t="n"/>
-      <c r="K34" s="12" t="n"/>
-      <c r="L34" s="28" t="n"/>
-      <c r="M34" s="12" t="n"/>
+      <c r="K34" s="28" t="n"/>
+      <c r="L34" s="12" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
@@ -27003,16 +26128,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H35" s="12" t="inlineStr"/>
-      <c r="I35" s="27" t="inlineStr">
+      <c r="H35" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I35" s="12" t="n"/>
       <c r="J35" s="12" t="n"/>
-      <c r="K35" s="12" t="n"/>
-      <c r="L35" s="28" t="n"/>
-      <c r="M35" s="12" t="n"/>
+      <c r="K35" s="28" t="n"/>
+      <c r="L35" s="12" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
@@ -27050,16 +26174,15 @@
           <t>Reopen is not shown.</t>
         </is>
       </c>
-      <c r="H36" s="12" t="inlineStr"/>
-      <c r="I36" s="27" t="inlineStr">
+      <c r="H36" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I36" s="12" t="n"/>
       <c r="J36" s="12" t="n"/>
-      <c r="K36" s="12" t="n"/>
-      <c r="L36" s="28" t="n"/>
-      <c r="M36" s="12" t="n"/>
+      <c r="K36" s="28" t="n"/>
+      <c r="L36" s="12" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
@@ -27097,16 +26220,15 @@
           <t>Reopen is not shown.</t>
         </is>
       </c>
-      <c r="H37" s="12" t="inlineStr"/>
-      <c r="I37" s="27" t="inlineStr">
+      <c r="H37" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I37" s="12" t="n"/>
       <c r="J37" s="12" t="n"/>
-      <c r="K37" s="12" t="n"/>
-      <c r="L37" s="28" t="n"/>
-      <c r="M37" s="12" t="n"/>
+      <c r="K37" s="28" t="n"/>
+      <c r="L37" s="12" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
@@ -27144,16 +26266,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H38" s="12" t="inlineStr"/>
-      <c r="I38" s="27" t="inlineStr">
+      <c r="H38" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I38" s="12" t="n"/>
       <c r="J38" s="12" t="n"/>
-      <c r="K38" s="12" t="n"/>
-      <c r="L38" s="28" t="n"/>
-      <c r="M38" s="12" t="n"/>
+      <c r="K38" s="28" t="n"/>
+      <c r="L38" s="12" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
@@ -27191,16 +26312,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H39" s="12" t="inlineStr"/>
-      <c r="I39" s="27" t="inlineStr">
+      <c r="H39" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I39" s="12" t="n"/>
       <c r="J39" s="12" t="n"/>
-      <c r="K39" s="12" t="n"/>
-      <c r="L39" s="28" t="n"/>
-      <c r="M39" s="12" t="n"/>
+      <c r="K39" s="28" t="n"/>
+      <c r="L39" s="12" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
@@ -27238,16 +26358,15 @@
           <t>Override Claimant is not shown.</t>
         </is>
       </c>
-      <c r="H40" s="12" t="inlineStr"/>
-      <c r="I40" s="27" t="inlineStr">
+      <c r="H40" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I40" s="12" t="n"/>
       <c r="J40" s="12" t="n"/>
-      <c r="K40" s="12" t="n"/>
-      <c r="L40" s="28" t="n"/>
-      <c r="M40" s="12" t="n"/>
+      <c r="K40" s="28" t="n"/>
+      <c r="L40" s="12" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
@@ -27285,16 +26404,15 @@
           <t>Override Claimant is not shown.</t>
         </is>
       </c>
-      <c r="H41" s="12" t="inlineStr"/>
-      <c r="I41" s="27" t="inlineStr">
+      <c r="H41" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I41" s="12" t="n"/>
       <c r="J41" s="12" t="n"/>
-      <c r="K41" s="12" t="n"/>
-      <c r="L41" s="28" t="n"/>
-      <c r="M41" s="12" t="n"/>
+      <c r="K41" s="28" t="n"/>
+      <c r="L41" s="12" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
@@ -27332,16 +26450,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H42" s="12" t="inlineStr"/>
-      <c r="I42" s="27" t="inlineStr">
+      <c r="H42" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I42" s="12" t="n"/>
       <c r="J42" s="12" t="n"/>
-      <c r="K42" s="12" t="n"/>
-      <c r="L42" s="28" t="n"/>
-      <c r="M42" s="12" t="n"/>
+      <c r="K42" s="28" t="n"/>
+      <c r="L42" s="12" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
@@ -27379,16 +26496,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H43" s="12" t="inlineStr"/>
-      <c r="I43" s="27" t="inlineStr">
+      <c r="H43" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I43" s="12" t="n"/>
       <c r="J43" s="12" t="n"/>
-      <c r="K43" s="12" t="n"/>
-      <c r="L43" s="28" t="n"/>
-      <c r="M43" s="12" t="n"/>
+      <c r="K43" s="28" t="n"/>
+      <c r="L43" s="12" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
@@ -27426,16 +26542,15 @@
           <t>Set Settlement is not shown.</t>
         </is>
       </c>
-      <c r="H44" s="12" t="inlineStr"/>
-      <c r="I44" s="27" t="inlineStr">
+      <c r="H44" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I44" s="12" t="n"/>
       <c r="J44" s="12" t="n"/>
-      <c r="K44" s="12" t="n"/>
-      <c r="L44" s="28" t="n"/>
-      <c r="M44" s="12" t="n"/>
+      <c r="K44" s="28" t="n"/>
+      <c r="L44" s="12" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
@@ -27473,16 +26588,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H45" s="12" t="inlineStr"/>
-      <c r="I45" s="27" t="inlineStr">
+      <c r="H45" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I45" s="12" t="n"/>
       <c r="J45" s="12" t="n"/>
-      <c r="K45" s="12" t="n"/>
-      <c r="L45" s="28" t="n"/>
-      <c r="M45" s="12" t="n"/>
+      <c r="K45" s="28" t="n"/>
+      <c r="L45" s="12" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
@@ -27520,16 +26634,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H46" s="12" t="inlineStr"/>
-      <c r="I46" s="27" t="inlineStr">
+      <c r="H46" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I46" s="12" t="n"/>
       <c r="J46" s="12" t="n"/>
-      <c r="K46" s="12" t="n"/>
-      <c r="L46" s="28" t="n"/>
-      <c r="M46" s="12" t="n"/>
+      <c r="K46" s="28" t="n"/>
+      <c r="L46" s="12" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
@@ -27567,16 +26680,15 @@
           <t>Assign Adjuster is not shown.</t>
         </is>
       </c>
-      <c r="H47" s="12" t="inlineStr"/>
-      <c r="I47" s="27" t="inlineStr">
+      <c r="H47" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I47" s="12" t="n"/>
       <c r="J47" s="12" t="n"/>
-      <c r="K47" s="12" t="n"/>
-      <c r="L47" s="28" t="n"/>
-      <c r="M47" s="12" t="n"/>
+      <c r="K47" s="28" t="n"/>
+      <c r="L47" s="12" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
@@ -27614,16 +26726,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H48" s="12" t="inlineStr"/>
-      <c r="I48" s="27" t="inlineStr">
+      <c r="H48" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I48" s="12" t="n"/>
       <c r="J48" s="12" t="n"/>
-      <c r="K48" s="12" t="n"/>
-      <c r="L48" s="28" t="n"/>
-      <c r="M48" s="12" t="n"/>
+      <c r="K48" s="28" t="n"/>
+      <c r="L48" s="12" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
@@ -27661,16 +26772,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H49" s="12" t="inlineStr"/>
-      <c r="I49" s="27" t="inlineStr">
+      <c r="H49" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I49" s="12" t="n"/>
       <c r="J49" s="12" t="n"/>
-      <c r="K49" s="12" t="n"/>
-      <c r="L49" s="28" t="n"/>
-      <c r="M49" s="12" t="n"/>
+      <c r="K49" s="28" t="n"/>
+      <c r="L49" s="12" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
@@ -27708,16 +26818,15 @@
           <t>Override Follow-up Date is not shown.</t>
         </is>
       </c>
-      <c r="H50" s="12" t="inlineStr"/>
-      <c r="I50" s="27" t="inlineStr">
+      <c r="H50" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I50" s="12" t="n"/>
       <c r="J50" s="12" t="n"/>
-      <c r="K50" s="12" t="n"/>
-      <c r="L50" s="28" t="n"/>
-      <c r="M50" s="12" t="n"/>
+      <c r="K50" s="28" t="n"/>
+      <c r="L50" s="12" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
@@ -27755,16 +26864,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H51" s="12" t="inlineStr"/>
-      <c r="I51" s="27" t="inlineStr">
+      <c r="H51" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I51" s="12" t="n"/>
       <c r="J51" s="12" t="n"/>
-      <c r="K51" s="12" t="n"/>
-      <c r="L51" s="28" t="n"/>
-      <c r="M51" s="12" t="n"/>
+      <c r="K51" s="28" t="n"/>
+      <c r="L51" s="12" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
@@ -27802,16 +26910,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H52" s="12" t="inlineStr"/>
-      <c r="I52" s="27" t="inlineStr">
+      <c r="H52" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I52" s="12" t="n"/>
       <c r="J52" s="12" t="n"/>
-      <c r="K52" s="12" t="n"/>
-      <c r="L52" s="28" t="n"/>
-      <c r="M52" s="12" t="n"/>
+      <c r="K52" s="28" t="n"/>
+      <c r="L52" s="12" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
@@ -27849,16 +26956,15 @@
           <t>Amend Reserve is not shown.</t>
         </is>
       </c>
-      <c r="H53" s="12" t="inlineStr"/>
-      <c r="I53" s="27" t="inlineStr">
+      <c r="H53" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I53" s="12" t="n"/>
       <c r="J53" s="12" t="n"/>
-      <c r="K53" s="12" t="n"/>
-      <c r="L53" s="28" t="n"/>
-      <c r="M53" s="12" t="n"/>
+      <c r="K53" s="28" t="n"/>
+      <c r="L53" s="12" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
@@ -27896,16 +27002,15 @@
           <t>Amend Reserve is not shown.</t>
         </is>
       </c>
-      <c r="H54" s="12" t="inlineStr"/>
-      <c r="I54" s="27" t="inlineStr">
+      <c r="H54" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I54" s="12" t="n"/>
       <c r="J54" s="12" t="n"/>
-      <c r="K54" s="12" t="n"/>
-      <c r="L54" s="28" t="n"/>
-      <c r="M54" s="12" t="n"/>
+      <c r="K54" s="28" t="n"/>
+      <c r="L54" s="12" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
@@ -27943,16 +27048,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H55" s="12" t="inlineStr"/>
-      <c r="I55" s="27" t="inlineStr">
+      <c r="H55" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I55" s="12" t="n"/>
       <c r="J55" s="12" t="n"/>
-      <c r="K55" s="12" t="n"/>
-      <c r="L55" s="28" t="n"/>
-      <c r="M55" s="12" t="n"/>
+      <c r="K55" s="28" t="n"/>
+      <c r="L55" s="12" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
@@ -27990,16 +27094,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H56" s="12" t="inlineStr"/>
-      <c r="I56" s="27" t="inlineStr">
+      <c r="H56" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I56" s="12" t="n"/>
       <c r="J56" s="12" t="n"/>
-      <c r="K56" s="12" t="n"/>
-      <c r="L56" s="28" t="n"/>
-      <c r="M56" s="12" t="n"/>
+      <c r="K56" s="28" t="n"/>
+      <c r="L56" s="12" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
@@ -28037,16 +27140,15 @@
           <t>Insurer Location References is not in the menu.</t>
         </is>
       </c>
-      <c r="H57" s="12" t="inlineStr"/>
-      <c r="I57" s="27" t="inlineStr">
+      <c r="H57" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I57" s="12" t="n"/>
       <c r="J57" s="12" t="n"/>
-      <c r="K57" s="12" t="n"/>
-      <c r="L57" s="28" t="n"/>
-      <c r="M57" s="12" t="n"/>
+      <c r="K57" s="28" t="n"/>
+      <c r="L57" s="12" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
@@ -28084,16 +27186,15 @@
           <t>Insurer Location References is not in the menu.</t>
         </is>
       </c>
-      <c r="H58" s="12" t="inlineStr"/>
-      <c r="I58" s="27" t="inlineStr">
+      <c r="H58" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I58" s="12" t="n"/>
       <c r="J58" s="12" t="n"/>
-      <c r="K58" s="12" t="n"/>
-      <c r="L58" s="28" t="n"/>
-      <c r="M58" s="12" t="n"/>
+      <c r="K58" s="28" t="n"/>
+      <c r="L58" s="12" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
@@ -28131,16 +27232,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H59" s="12" t="inlineStr"/>
-      <c r="I59" s="27" t="inlineStr">
+      <c r="H59" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I59" s="12" t="n"/>
       <c r="J59" s="12" t="n"/>
-      <c r="K59" s="12" t="n"/>
-      <c r="L59" s="28" t="n"/>
-      <c r="M59" s="12" t="n"/>
+      <c r="K59" s="28" t="n"/>
+      <c r="L59" s="12" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="12" t="inlineStr">
@@ -28178,16 +27278,15 @@
           <t>Claims Setup is not in the menu; the Claims lists are read only.</t>
         </is>
       </c>
-      <c r="H60" s="12" t="inlineStr"/>
-      <c r="I60" s="27" t="inlineStr">
+      <c r="H60" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I60" s="12" t="n"/>
       <c r="J60" s="12" t="n"/>
-      <c r="K60" s="12" t="n"/>
-      <c r="L60" s="28" t="n"/>
-      <c r="M60" s="12" t="n"/>
+      <c r="K60" s="28" t="n"/>
+      <c r="L60" s="12" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="12" t="inlineStr">
@@ -28225,16 +27324,15 @@
           <t>Claims Setup is not in the menu; the Claims lists are read only.</t>
         </is>
       </c>
-      <c r="H61" s="12" t="inlineStr"/>
-      <c r="I61" s="27" t="inlineStr">
+      <c r="H61" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I61" s="12" t="n"/>
       <c r="J61" s="12" t="n"/>
-      <c r="K61" s="12" t="n"/>
-      <c r="L61" s="28" t="n"/>
-      <c r="M61" s="12" t="n"/>
+      <c r="K61" s="28" t="n"/>
+      <c r="L61" s="12" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
@@ -28272,16 +27370,15 @@
           <t>Claims Setup is not in the menu; the Claims lists are read only.</t>
         </is>
       </c>
-      <c r="H62" s="12" t="inlineStr"/>
-      <c r="I62" s="27" t="inlineStr">
+      <c r="H62" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I62" s="12" t="n"/>
       <c r="J62" s="12" t="n"/>
-      <c r="K62" s="12" t="n"/>
-      <c r="L62" s="28" t="n"/>
-      <c r="M62" s="12" t="n"/>
+      <c r="K62" s="28" t="n"/>
+      <c r="L62" s="12" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="12" t="inlineStr">
@@ -28319,16 +27416,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H63" s="12" t="inlineStr"/>
-      <c r="I63" s="27" t="inlineStr">
+      <c r="H63" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I63" s="12" t="n"/>
       <c r="J63" s="12" t="n"/>
-      <c r="K63" s="12" t="n"/>
-      <c r="L63" s="28" t="n"/>
-      <c r="M63" s="12" t="n"/>
+      <c r="K63" s="28" t="n"/>
+      <c r="L63" s="12" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="12" t="inlineStr">
@@ -28366,16 +27462,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H64" s="12" t="inlineStr"/>
-      <c r="I64" s="27" t="inlineStr">
+      <c r="H64" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I64" s="12" t="n"/>
       <c r="J64" s="12" t="n"/>
-      <c r="K64" s="12" t="n"/>
-      <c r="L64" s="28" t="n"/>
-      <c r="M64" s="12" t="n"/>
+      <c r="K64" s="28" t="n"/>
+      <c r="L64" s="12" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
@@ -28413,16 +27508,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H65" s="12" t="inlineStr"/>
-      <c r="I65" s="27" t="inlineStr">
+      <c r="H65" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I65" s="12" t="n"/>
       <c r="J65" s="12" t="n"/>
-      <c r="K65" s="12" t="n"/>
-      <c r="L65" s="28" t="n"/>
-      <c r="M65" s="12" t="n"/>
+      <c r="K65" s="28" t="n"/>
+      <c r="L65" s="12" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="12" t="inlineStr">
@@ -28460,16 +27554,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H66" s="12" t="inlineStr"/>
-      <c r="I66" s="27" t="inlineStr">
+      <c r="H66" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I66" s="12" t="n"/>
       <c r="J66" s="12" t="n"/>
-      <c r="K66" s="12" t="n"/>
-      <c r="L66" s="28" t="n"/>
-      <c r="M66" s="12" t="n"/>
+      <c r="K66" s="28" t="n"/>
+      <c r="L66" s="12" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="12" t="inlineStr">
@@ -28507,16 +27600,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H67" s="12" t="inlineStr"/>
-      <c r="I67" s="27" t="inlineStr">
+      <c r="H67" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I67" s="12" t="n"/>
       <c r="J67" s="12" t="n"/>
-      <c r="K67" s="12" t="n"/>
-      <c r="L67" s="28" t="n"/>
-      <c r="M67" s="12" t="n"/>
+      <c r="K67" s="28" t="n"/>
+      <c r="L67" s="12" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="12" t="inlineStr">
@@ -28554,16 +27646,15 @@
           <t>The category Claims Handling is not listed.</t>
         </is>
       </c>
-      <c r="H68" s="12" t="inlineStr"/>
-      <c r="I68" s="27" t="inlineStr">
+      <c r="H68" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I68" s="12" t="n"/>
       <c r="J68" s="12" t="n"/>
-      <c r="K68" s="12" t="n"/>
-      <c r="L68" s="28" t="n"/>
-      <c r="M68" s="12" t="n"/>
+      <c r="K68" s="28" t="n"/>
+      <c r="L68" s="12" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="12" t="inlineStr">
@@ -28601,16 +27692,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H69" s="12" t="inlineStr"/>
-      <c r="I69" s="27" t="inlineStr">
+      <c r="H69" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I69" s="12" t="n"/>
       <c r="J69" s="12" t="n"/>
-      <c r="K69" s="12" t="n"/>
-      <c r="L69" s="28" t="n"/>
-      <c r="M69" s="12" t="n"/>
+      <c r="K69" s="28" t="n"/>
+      <c r="L69" s="12" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="12" t="inlineStr">
@@ -28648,16 +27738,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H70" s="12" t="inlineStr"/>
-      <c r="I70" s="27" t="inlineStr">
+      <c r="H70" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I70" s="12" t="n"/>
       <c r="J70" s="12" t="n"/>
-      <c r="K70" s="12" t="n"/>
-      <c r="L70" s="28" t="n"/>
-      <c r="M70" s="12" t="n"/>
+      <c r="K70" s="28" t="n"/>
+      <c r="L70" s="12" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="12" t="inlineStr">
@@ -28695,16 +27784,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H71" s="12" t="inlineStr"/>
-      <c r="I71" s="27" t="inlineStr">
+      <c r="H71" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I71" s="12" t="n"/>
       <c r="J71" s="12" t="n"/>
-      <c r="K71" s="12" t="n"/>
-      <c r="L71" s="28" t="n"/>
-      <c r="M71" s="12" t="n"/>
+      <c r="K71" s="28" t="n"/>
+      <c r="L71" s="12" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="12" t="inlineStr">
@@ -28739,19 +27827,18 @@
       </c>
       <c r="G72" s="12" t="inlineStr">
         <is>
-          <t>Export is not shown; the export call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H72" s="12" t="inlineStr"/>
-      <c r="I72" s="27" t="inlineStr">
+          <t>Export is not shown; a direct export request is refused.</t>
+        </is>
+      </c>
+      <c r="H72" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I72" s="12" t="n"/>
       <c r="J72" s="12" t="n"/>
-      <c r="K72" s="12" t="n"/>
-      <c r="L72" s="28" t="n"/>
-      <c r="M72" s="12" t="n"/>
+      <c r="K72" s="28" t="n"/>
+      <c r="L72" s="12" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="12" t="inlineStr">
@@ -28786,19 +27873,18 @@
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
-          <t>Export is not shown; the export call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H73" s="12" t="inlineStr"/>
-      <c r="I73" s="27" t="inlineStr">
+          <t>Export is not shown; a direct export request is refused.</t>
+        </is>
+      </c>
+      <c r="H73" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I73" s="12" t="n"/>
       <c r="J73" s="12" t="n"/>
-      <c r="K73" s="12" t="n"/>
-      <c r="L73" s="28" t="n"/>
-      <c r="M73" s="12" t="n"/>
+      <c r="K73" s="28" t="n"/>
+      <c r="L73" s="12" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="12" t="inlineStr">
@@ -28833,19 +27919,18 @@
       </c>
       <c r="G74" s="12" t="inlineStr">
         <is>
-          <t>Export is not shown; the export call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H74" s="12" t="inlineStr"/>
-      <c r="I74" s="27" t="inlineStr">
+          <t>Export is not shown; a direct export request is refused.</t>
+        </is>
+      </c>
+      <c r="H74" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I74" s="12" t="n"/>
       <c r="J74" s="12" t="n"/>
-      <c r="K74" s="12" t="n"/>
-      <c r="L74" s="28" t="n"/>
-      <c r="M74" s="12" t="n"/>
+      <c r="K74" s="28" t="n"/>
+      <c r="L74" s="12" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="12" t="inlineStr">
@@ -28883,16 +27968,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H75" s="12" t="inlineStr"/>
-      <c r="I75" s="27" t="inlineStr">
+      <c r="H75" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I75" s="12" t="n"/>
       <c r="J75" s="12" t="n"/>
-      <c r="K75" s="12" t="n"/>
-      <c r="L75" s="28" t="n"/>
-      <c r="M75" s="12" t="n"/>
+      <c r="K75" s="28" t="n"/>
+      <c r="L75" s="12" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="12" t="inlineStr">
@@ -28930,16 +28014,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H76" s="12" t="inlineStr"/>
-      <c r="I76" s="27" t="inlineStr">
+      <c r="H76" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I76" s="12" t="n"/>
       <c r="J76" s="12" t="n"/>
-      <c r="K76" s="12" t="n"/>
-      <c r="L76" s="28" t="n"/>
-      <c r="M76" s="12" t="n"/>
+      <c r="K76" s="28" t="n"/>
+      <c r="L76" s="12" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="12" t="inlineStr">
@@ -28977,16 +28060,15 @@
           <t>BCL-DATA-EXTRACT is not listed.</t>
         </is>
       </c>
-      <c r="H77" s="12" t="inlineStr"/>
-      <c r="I77" s="27" t="inlineStr">
+      <c r="H77" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I77" s="12" t="n"/>
       <c r="J77" s="12" t="n"/>
-      <c r="K77" s="12" t="n"/>
-      <c r="L77" s="28" t="n"/>
-      <c r="M77" s="12" t="n"/>
+      <c r="K77" s="28" t="n"/>
+      <c r="L77" s="12" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="12" t="inlineStr">
@@ -29024,16 +28106,15 @@
           <t>BCL-DATA-EXTRACT is not listed.</t>
         </is>
       </c>
-      <c r="H78" s="12" t="inlineStr"/>
-      <c r="I78" s="27" t="inlineStr">
+      <c r="H78" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I78" s="12" t="n"/>
       <c r="J78" s="12" t="n"/>
-      <c r="K78" s="12" t="n"/>
-      <c r="L78" s="28" t="n"/>
-      <c r="M78" s="12" t="n"/>
+      <c r="K78" s="28" t="n"/>
+      <c r="L78" s="12" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="12" t="inlineStr">
@@ -29071,16 +28152,15 @@
           <t>BCL-DATA-EXTRACT is not listed.</t>
         </is>
       </c>
-      <c r="H79" s="12" t="inlineStr"/>
-      <c r="I79" s="27" t="inlineStr">
+      <c r="H79" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I79" s="12" t="n"/>
       <c r="J79" s="12" t="n"/>
-      <c r="K79" s="12" t="n"/>
-      <c r="L79" s="28" t="n"/>
-      <c r="M79" s="12" t="n"/>
+      <c r="K79" s="28" t="n"/>
+      <c r="L79" s="12" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="12" t="inlineStr">
@@ -29118,16 +28198,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H80" s="12" t="inlineStr"/>
-      <c r="I80" s="27" t="inlineStr">
+      <c r="H80" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I80" s="12" t="n"/>
       <c r="J80" s="12" t="n"/>
-      <c r="K80" s="12" t="n"/>
-      <c r="L80" s="28" t="n"/>
-      <c r="M80" s="12" t="n"/>
+      <c r="K80" s="28" t="n"/>
+      <c r="L80" s="12" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="12" t="inlineStr">
@@ -29165,16 +28244,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H81" s="12" t="inlineStr"/>
-      <c r="I81" s="27" t="inlineStr">
+      <c r="H81" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I81" s="12" t="n"/>
       <c r="J81" s="12" t="n"/>
-      <c r="K81" s="12" t="n"/>
-      <c r="L81" s="28" t="n"/>
-      <c r="M81" s="12" t="n"/>
+      <c r="K81" s="28" t="n"/>
+      <c r="L81" s="12" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="12" t="inlineStr">
@@ -29212,16 +28290,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H82" s="12" t="inlineStr"/>
-      <c r="I82" s="27" t="inlineStr">
+      <c r="H82" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I82" s="12" t="n"/>
       <c r="J82" s="12" t="n"/>
-      <c r="K82" s="12" t="n"/>
-      <c r="L82" s="28" t="n"/>
-      <c r="M82" s="12" t="n"/>
+      <c r="K82" s="28" t="n"/>
+      <c r="L82" s="12" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="12" t="inlineStr">
@@ -29259,16 +28336,15 @@
           <t>Reassign is not shown.</t>
         </is>
       </c>
-      <c r="H83" s="12" t="inlineStr"/>
-      <c r="I83" s="27" t="inlineStr">
+      <c r="H83" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I83" s="12" t="n"/>
       <c r="J83" s="12" t="n"/>
-      <c r="K83" s="12" t="n"/>
-      <c r="L83" s="28" t="n"/>
-      <c r="M83" s="12" t="n"/>
+      <c r="K83" s="28" t="n"/>
+      <c r="L83" s="12" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="12" t="inlineStr">
@@ -29306,16 +28382,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H84" s="12" t="inlineStr"/>
-      <c r="I84" s="27" t="inlineStr">
+      <c r="H84" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I84" s="12" t="n"/>
       <c r="J84" s="12" t="n"/>
-      <c r="K84" s="12" t="n"/>
-      <c r="L84" s="28" t="n"/>
-      <c r="M84" s="12" t="n"/>
+      <c r="K84" s="28" t="n"/>
+      <c r="L84" s="12" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="12" t="inlineStr">
@@ -29353,16 +28428,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H85" s="12" t="inlineStr"/>
-      <c r="I85" s="27" t="inlineStr">
+      <c r="H85" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I85" s="12" t="n"/>
       <c r="J85" s="12" t="n"/>
-      <c r="K85" s="12" t="n"/>
-      <c r="L85" s="28" t="n"/>
-      <c r="M85" s="12" t="n"/>
+      <c r="K85" s="28" t="n"/>
+      <c r="L85" s="12" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="12" t="inlineStr">
@@ -29400,16 +28474,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H86" s="12" t="inlineStr"/>
-      <c r="I86" s="27" t="inlineStr">
+      <c r="H86" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I86" s="12" t="n"/>
       <c r="J86" s="12" t="n"/>
-      <c r="K86" s="12" t="n"/>
-      <c r="L86" s="28" t="n"/>
-      <c r="M86" s="12" t="n"/>
+      <c r="K86" s="28" t="n"/>
+      <c r="L86" s="12" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="12" t="inlineStr">
@@ -29447,16 +28520,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H87" s="12" t="inlineStr"/>
-      <c r="I87" s="27" t="inlineStr">
+      <c r="H87" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I87" s="12" t="n"/>
       <c r="J87" s="12" t="n"/>
-      <c r="K87" s="12" t="n"/>
-      <c r="L87" s="28" t="n"/>
-      <c r="M87" s="12" t="n"/>
+      <c r="K87" s="28" t="n"/>
+      <c r="L87" s="12" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="12" t="inlineStr">
@@ -29494,16 +28566,15 @@
           <t>Claims Worklist is not in the menu; a claim address shows the no-access page.</t>
         </is>
       </c>
-      <c r="H88" s="12" t="inlineStr"/>
-      <c r="I88" s="27" t="inlineStr">
+      <c r="H88" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I88" s="12" t="n"/>
       <c r="J88" s="12" t="n"/>
-      <c r="K88" s="12" t="n"/>
-      <c r="L88" s="28" t="n"/>
-      <c r="M88" s="12" t="n"/>
+      <c r="K88" s="28" t="n"/>
+      <c r="L88" s="12" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="12" t="inlineStr">
@@ -29541,23 +28612,22 @@
           <t>Claims Worklist is not in the menu; a claim address shows the no-access page.</t>
         </is>
       </c>
-      <c r="H89" s="12" t="inlineStr"/>
-      <c r="I89" s="27" t="inlineStr">
+      <c r="H89" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I89" s="12" t="n"/>
       <c r="J89" s="12" t="n"/>
-      <c r="K89" s="12" t="n"/>
-      <c r="L89" s="28" t="n"/>
-      <c r="M89" s="12" t="n"/>
+      <c r="K89" s="28" t="n"/>
+      <c r="L89" s="12" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:M89"/>
+  <autoFilter ref="A4:L89"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A2:L2"/>
   </mergeCells>
-  <conditionalFormatting sqref="I5:I589">
+  <conditionalFormatting sqref="H5:H589">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="1" stopIfTrue="1">
       <formula>"Pass"</formula>
     </cfRule>
@@ -29571,7 +28641,7 @@
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:M589">
+  <conditionalFormatting sqref="A5:L589">
     <cfRule type="expression" priority="5" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
@@ -29580,7 +28650,7 @@
     <dataValidation sqref="F5:F589" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Access" error="Choose a value from the list (Access)." type="list">
       <formula1>'_lists'!$F$1:$F$2</formula1>
     </dataValidation>
-    <dataValidation sqref="I5:I589" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
+    <dataValidation sqref="H5:H589" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
       <formula1>'_lists'!$G$1:$G$5</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/deliverables/out/Drop-2_Independent/BRD-07_Claims/BIBS_TestPlan_BRD-07_Claims_v1.0.xlsx
+++ b/docs/deliverables/out/Drop-2_Independent/BRD-07_Claims/BIBS_TestPlan_BRD-07_Claims_v1.0.xlsx
@@ -4931,7 +4931,7 @@
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>The status list offers the 18 BRD values on a new database, each with phase, waiting party, follow-up days and the awaiting-remittance flag.</t>
+          <t>The status list offers the 18 BRD values when BIBS is first set up, each with phase, waiting party, follow-up days and the awaiting-remittance flag.</t>
         </is>
       </c>
       <c r="E74" s="12" t="inlineStr">
@@ -7766,8 +7766,8 @@
       </c>
       <c r="K7" s="12" t="inlineStr">
         <is>
-          <t>The account is locked after the third attempt and the fourth attempt is refused.
-Message "Account is locked. Contact your administrator.".</t>
+          <t>The account is locked after the third attempt; the fourth attempt, with the correct password, is refused with the same message as a wrong password; the lock shows to the System Administrator in Administration &gt; Users.
+Message "Invalid user name or password".</t>
         </is>
       </c>
       <c r="L7" s="12" t="inlineStr">
@@ -8325,7 +8325,7 @@
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I15" s="12" t="inlineStr">
@@ -8609,7 +8609,7 @@
       </c>
       <c r="H19" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I19" s="12" t="inlineStr">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="H58" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I58" s="12" t="inlineStr">
@@ -14890,7 +14890,7 @@
       </c>
       <c r="H107" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I107" s="12" t="inlineStr">
@@ -20523,7 +20523,7 @@
       </c>
       <c r="H186" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I186" s="12" t="inlineStr">
@@ -24468,7 +24468,7 @@
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Recorded on SIT by the test lead; reported dates set in the test database for ageing</t>
+          <t>Recorded on SIT by the test lead; reported dates set in the test environment for ageing</t>
         </is>
       </c>
       <c r="E9" s="12" t="n">
